--- a/ProductFaangCodingPractice/ProblemSolvingList_ONLY_FOCUS.xlsx
+++ b/ProductFaangCodingPractice/ProblemSolvingList_ONLY_FOCUS.xlsx
@@ -29,7 +29,7 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -1319,6 +1319,12 @@
       <sz val="11"/>
       <color rgb="FFffffff"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -1359,12 +1365,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Open Sans"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -1484,7 +1484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1495,22 +1495,22 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
@@ -1519,35 +1519,32 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1576,20 +1573,17 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1896,31 +1890,31 @@
   <dimension ref="A1:Y1002"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="32" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="32" width="12.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="33" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="32" width="36.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="34" width="20.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="34" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="35" width="39.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="34" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="31" width="15.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="31" width="12.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="32" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="31" width="36.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="33" width="20.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="33" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="31" width="39.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="33" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -3227,16 +3221,16 @@
       <c r="C35" s="2">
         <v>1</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="23" t="s">
+      <c r="G35" s="22" t="s">
         <v>15</v>
       </c>
       <c r="H35" s="16" t="s">
@@ -3268,10 +3262,10 @@
       <c r="C36" s="2">
         <v>2</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F36" s="17" t="s">
@@ -3307,10 +3301,10 @@
       <c r="C37" s="2">
         <v>3</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="17" t="s">
@@ -3346,10 +3340,10 @@
       <c r="C38" s="2">
         <v>4</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="17" t="s">
@@ -3387,10 +3381,10 @@
       <c r="C39" s="2">
         <v>5</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E39" s="22" t="s">
+      <c r="E39" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="17" t="s">
@@ -3426,10 +3420,10 @@
       <c r="C40" s="2">
         <v>6</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="E40" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F40" s="17" t="s">
@@ -3470,7 +3464,7 @@
       <c r="D41" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E41" s="22" t="s">
+      <c r="E41" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F41" s="19" t="s">
@@ -3565,7 +3559,7 @@
       <c r="D44" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E44" s="22" t="s">
+      <c r="E44" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="15" t="s">
@@ -3606,7 +3600,7 @@
       <c r="D45" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E45" s="22" t="s">
+      <c r="E45" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F45" s="15" t="s">
@@ -3645,7 +3639,7 @@
       <c r="D46" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E46" s="22" t="s">
+      <c r="E46" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F46" s="15" t="s">
@@ -3684,7 +3678,7 @@
       <c r="D47" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E47" s="22" t="s">
+      <c r="E47" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="17" t="s">
@@ -3723,7 +3717,7 @@
       <c r="D48" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F48" s="17" t="s">
@@ -3762,7 +3756,7 @@
       <c r="D49" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E49" s="22" t="s">
+      <c r="E49" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="17" t="s">
@@ -3803,7 +3797,7 @@
       <c r="D50" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E50" s="22" t="s">
+      <c r="E50" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F50" s="17" t="s">
@@ -3842,7 +3836,7 @@
       <c r="D51" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E51" s="22" t="s">
+      <c r="E51" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F51" s="17" t="s">
@@ -3881,7 +3875,7 @@
       <c r="D52" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E52" s="22" t="s">
+      <c r="E52" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F52" s="19" t="s">
@@ -3920,7 +3914,7 @@
       <c r="D53" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E53" s="22" t="s">
+      <c r="E53" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F53" s="19" t="s">
@@ -3984,7 +3978,7 @@
       <c r="Y54" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
-      <c r="A55" s="24"/>
+      <c r="A55" s="23"/>
       <c r="B55" s="6"/>
       <c r="C55" s="2"/>
       <c r="D55" s="5"/>
@@ -4038,7 +4032,7 @@
       <c r="Y56" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
-      <c r="A57" s="25" t="s">
+      <c r="A57" s="24" t="s">
         <v>99</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -4050,7 +4044,7 @@
       <c r="D57" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F57" s="17" t="s">
@@ -4059,7 +4053,7 @@
       <c r="G57" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H57" s="26" t="s">
+      <c r="H57" s="25" t="s">
         <v>101</v>
       </c>
       <c r="I57" s="6"/>
@@ -4091,14 +4085,14 @@
       <c r="D58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E58" s="22" t="s">
+      <c r="E58" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G58" s="6"/>
-      <c r="H58" s="26" t="s">
+      <c r="H58" s="25" t="s">
         <v>103</v>
       </c>
       <c r="I58" s="6"/>
@@ -4130,7 +4124,7 @@
       <c r="D59" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E59" s="22" t="s">
+      <c r="E59" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F59" s="17" t="s">
@@ -4139,7 +4133,7 @@
       <c r="G59" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H59" s="26" t="s">
+      <c r="H59" s="25" t="s">
         <v>105</v>
       </c>
       <c r="I59" s="6"/>
@@ -4171,14 +4165,14 @@
       <c r="D60" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E60" s="22" t="s">
+      <c r="E60" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G60" s="6"/>
-      <c r="H60" s="26" t="s">
+      <c r="H60" s="25" t="s">
         <v>107</v>
       </c>
       <c r="I60" s="6"/>
@@ -4210,14 +4204,14 @@
       <c r="D61" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E61" s="22" t="s">
+      <c r="E61" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G61" s="6"/>
-      <c r="H61" s="26" t="s">
+      <c r="H61" s="25" t="s">
         <v>109</v>
       </c>
       <c r="I61" s="6"/>
@@ -4249,7 +4243,7 @@
       <c r="D62" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E62" s="22" t="s">
+      <c r="E62" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F62" s="17" t="s">
@@ -4258,7 +4252,7 @@
       <c r="G62" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H62" s="26" t="s">
+      <c r="H62" s="25" t="s">
         <v>18</v>
       </c>
       <c r="I62" s="6"/>
@@ -4290,7 +4284,7 @@
       <c r="D63" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E63" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F63" s="17" t="s">
@@ -4299,7 +4293,7 @@
       <c r="G63" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H63" s="27" t="s">
+      <c r="H63" s="26" t="s">
         <v>112</v>
       </c>
       <c r="I63" s="6"/>
@@ -4331,14 +4325,14 @@
       <c r="D64" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E64" s="22" t="s">
+      <c r="E64" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F64" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G64" s="6"/>
-      <c r="H64" s="26" t="s">
+      <c r="H64" s="25" t="s">
         <v>113</v>
       </c>
       <c r="I64" s="6"/>
@@ -4370,7 +4364,7 @@
       <c r="D65" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F65" s="19" t="s">
@@ -4379,7 +4373,7 @@
       <c r="G65" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H65" s="26" t="s">
+      <c r="H65" s="25" t="s">
         <v>115</v>
       </c>
       <c r="I65" s="6"/>
@@ -4411,7 +4405,7 @@
       <c r="D66" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F66" s="19" t="s">
@@ -4420,7 +4414,7 @@
       <c r="G66" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H66" s="27" t="s">
+      <c r="H66" s="26" t="s">
         <v>117</v>
       </c>
       <c r="I66" s="6"/>
@@ -4452,14 +4446,14 @@
       <c r="D67" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F67" s="19" t="s">
         <v>63</v>
       </c>
       <c r="G67" s="6"/>
-      <c r="H67" s="27" t="s">
+      <c r="H67" s="26" t="s">
         <v>118</v>
       </c>
       <c r="I67" s="6"/>
@@ -4480,7 +4474,7 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="2"/>
@@ -4507,7 +4501,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="2"/>
@@ -4534,8 +4528,8 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
-      <c r="A70" s="25" t="s">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
+      <c r="A70" s="24" t="s">
         <v>119</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -4547,7 +4541,7 @@
       <c r="D70" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E70" s="22" t="s">
+      <c r="E70" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F70" s="15" t="s">
@@ -4556,7 +4550,7 @@
       <c r="G70" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H70" s="26" t="s">
+      <c r="H70" s="25" t="s">
         <v>121</v>
       </c>
       <c r="I70" s="6"/>
@@ -4577,7 +4571,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
       <c r="A71" s="5"/>
       <c r="B71" s="6" t="s">
         <v>11</v>
@@ -4588,7 +4582,7 @@
       <c r="D71" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E71" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F71" s="15" t="s">
@@ -4597,7 +4591,7 @@
       <c r="G71" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H71" s="26" t="s">
+      <c r="H71" s="25" t="s">
         <v>123</v>
       </c>
       <c r="I71" s="6"/>
@@ -4618,7 +4612,7 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="5"/>
       <c r="B72" s="6" t="s">
         <v>11</v>
@@ -4629,7 +4623,7 @@
       <c r="D72" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F72" s="15" t="s">
@@ -4638,7 +4632,7 @@
       <c r="G72" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H72" s="26" t="s">
+      <c r="H72" s="25" t="s">
         <v>125</v>
       </c>
       <c r="I72" s="6"/>
@@ -4659,7 +4653,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
       <c r="A73" s="5"/>
       <c r="B73" s="6" t="s">
         <v>11</v>
@@ -4670,14 +4664,14 @@
       <c r="D73" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F73" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G73" s="6"/>
-      <c r="H73" s="26" t="s">
+      <c r="H73" s="25" t="s">
         <v>127</v>
       </c>
       <c r="I73" s="6"/>
@@ -4698,7 +4692,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="5"/>
       <c r="B74" s="6" t="s">
         <v>11</v>
@@ -4709,7 +4703,7 @@
       <c r="D74" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F74" s="15" t="s">
@@ -4718,7 +4712,7 @@
       <c r="G74" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H74" s="26" t="s">
+      <c r="H74" s="25" t="s">
         <v>129</v>
       </c>
       <c r="I74" s="6"/>
@@ -4739,7 +4733,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="5"/>
       <c r="B75" s="6" t="s">
         <v>11</v>
@@ -4750,7 +4744,7 @@
       <c r="D75" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E75" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F75" s="17" t="s">
@@ -4759,7 +4753,7 @@
       <c r="G75" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H75" s="26" t="s">
+      <c r="H75" s="25" t="s">
         <v>131</v>
       </c>
       <c r="I75" s="6"/>
@@ -4780,7 +4774,7 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="5"/>
       <c r="B76" s="6" t="s">
         <v>11</v>
@@ -4791,7 +4785,7 @@
       <c r="D76" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E76" s="22" t="s">
+      <c r="E76" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F76" s="17" t="s">
@@ -4800,7 +4794,7 @@
       <c r="G76" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H76" s="27" t="s">
+      <c r="H76" s="26" t="s">
         <v>133</v>
       </c>
       <c r="I76" s="6"/>
@@ -4821,7 +4815,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="5"/>
       <c r="B77" s="6" t="s">
         <v>11</v>
@@ -4832,7 +4826,7 @@
       <c r="D77" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="E77" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F77" s="17" t="s">
@@ -4841,7 +4835,7 @@
       <c r="G77" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H77" s="26" t="s">
+      <c r="H77" s="25" t="s">
         <v>135</v>
       </c>
       <c r="I77" s="6"/>
@@ -4862,7 +4856,7 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="5"/>
       <c r="B78" s="6" t="s">
         <v>11</v>
@@ -4873,14 +4867,14 @@
       <c r="D78" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E78" s="22" t="s">
+      <c r="E78" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F78" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G78" s="6"/>
-      <c r="H78" s="27" t="s">
+      <c r="H78" s="26" t="s">
         <v>137</v>
       </c>
       <c r="I78" s="6"/>
@@ -4901,7 +4895,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="5"/>
       <c r="B79" s="6" t="s">
         <v>11</v>
@@ -4912,14 +4906,14 @@
       <c r="D79" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E79" s="22" t="s">
+      <c r="E79" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G79" s="6"/>
-      <c r="H79" s="26" t="s">
+      <c r="H79" s="25" t="s">
         <v>139</v>
       </c>
       <c r="I79" s="6"/>
@@ -4940,7 +4934,7 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
       <c r="A80" s="5"/>
       <c r="B80" s="6" t="s">
         <v>11</v>
@@ -4951,7 +4945,7 @@
       <c r="D80" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E80" s="22" t="s">
+      <c r="E80" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F80" s="17" t="s">
@@ -4960,7 +4954,7 @@
       <c r="G80" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H80" s="27" t="s">
+      <c r="H80" s="26" t="s">
         <v>141</v>
       </c>
       <c r="I80" s="6"/>
@@ -4981,7 +4975,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
       <c r="A81" s="5"/>
       <c r="B81" s="6" t="s">
         <v>11</v>
@@ -4992,14 +4986,14 @@
       <c r="D81" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E81" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F81" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G81" s="6"/>
-      <c r="H81" s="27" t="s">
+      <c r="H81" s="26" t="s">
         <v>143</v>
       </c>
       <c r="I81" s="6"/>
@@ -5020,7 +5014,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
       <c r="A82" s="5"/>
       <c r="B82" s="6" t="s">
         <v>11</v>
@@ -5031,7 +5025,7 @@
       <c r="D82" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E82" s="22" t="s">
+      <c r="E82" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F82" s="19" t="s">
@@ -5040,7 +5034,7 @@
       <c r="G82" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H82" s="27" t="s">
+      <c r="H82" s="26" t="s">
         <v>145</v>
       </c>
       <c r="I82" s="6"/>
@@ -5061,7 +5055,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="2"/>
@@ -5088,7 +5082,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="2"/>
@@ -5115,8 +5109,8 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
-      <c r="A85" s="28" t="s">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
+      <c r="A85" s="27" t="s">
         <v>146</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -5128,7 +5122,7 @@
       <c r="D85" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E85" s="22" t="s">
+      <c r="E85" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F85" s="15" t="s">
@@ -5137,7 +5131,7 @@
       <c r="G85" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H85" s="26" t="s">
+      <c r="H85" s="25" t="s">
         <v>148</v>
       </c>
       <c r="I85" s="6"/>
@@ -5158,7 +5152,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
       <c r="A86" s="5"/>
       <c r="B86" s="6" t="s">
         <v>11</v>
@@ -5169,7 +5163,7 @@
       <c r="D86" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E86" s="22" t="s">
+      <c r="E86" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F86" s="15" t="s">
@@ -5178,7 +5172,7 @@
       <c r="G86" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H86" s="27" t="s">
+      <c r="H86" s="26" t="s">
         <v>150</v>
       </c>
       <c r="I86" s="6"/>
@@ -5199,7 +5193,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
       <c r="A87" s="5"/>
       <c r="B87" s="6" t="s">
         <v>11</v>
@@ -5210,7 +5204,7 @@
       <c r="D87" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E87" s="22" t="s">
+      <c r="E87" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F87" s="15" t="s">
@@ -5219,7 +5213,7 @@
       <c r="G87" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H87" s="26" t="s">
+      <c r="H87" s="25" t="s">
         <v>152</v>
       </c>
       <c r="I87" s="6"/>
@@ -5240,7 +5234,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
       <c r="A88" s="5"/>
       <c r="B88" s="6" t="s">
         <v>11</v>
@@ -5251,7 +5245,7 @@
       <c r="D88" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E88" s="22" t="s">
+      <c r="E88" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F88" s="15" t="s">
@@ -5260,7 +5254,7 @@
       <c r="G88" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H88" s="26" t="s">
+      <c r="H88" s="25" t="s">
         <v>154</v>
       </c>
       <c r="I88" s="6"/>
@@ -5281,7 +5275,7 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
       <c r="A89" s="5"/>
       <c r="B89" s="6" t="s">
         <v>11</v>
@@ -5292,7 +5286,7 @@
       <c r="D89" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E89" s="22" t="s">
+      <c r="E89" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F89" s="15" t="s">
@@ -5301,7 +5295,7 @@
       <c r="G89" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H89" s="26" t="s">
+      <c r="H89" s="25" t="s">
         <v>156</v>
       </c>
       <c r="I89" s="6"/>
@@ -5322,7 +5316,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
       <c r="A90" s="5"/>
       <c r="B90" s="6" t="s">
         <v>11</v>
@@ -5333,14 +5327,14 @@
       <c r="D90" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E90" s="22" t="s">
+      <c r="E90" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F90" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G90" s="6"/>
-      <c r="H90" s="26" t="s">
+      <c r="H90" s="25" t="s">
         <v>158</v>
       </c>
       <c r="I90" s="6"/>
@@ -5372,14 +5366,14 @@
       <c r="D91" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E91" s="22" t="s">
+      <c r="E91" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F91" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G91" s="6"/>
-      <c r="H91" s="27" t="s">
+      <c r="H91" s="26" t="s">
         <v>160</v>
       </c>
       <c r="I91" s="6"/>
@@ -5420,7 +5414,7 @@
       <c r="G92" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H92" s="26" t="s">
+      <c r="H92" s="25" t="s">
         <v>162</v>
       </c>
       <c r="I92" s="6"/>
@@ -5452,7 +5446,7 @@
       <c r="D93" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E93" s="22" t="s">
+      <c r="E93" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F93" s="17" t="s">
@@ -5461,7 +5455,7 @@
       <c r="G93" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H93" s="26" t="s">
+      <c r="H93" s="25" t="s">
         <v>164</v>
       </c>
       <c r="I93" s="6"/>
@@ -5493,7 +5487,7 @@
       <c r="D94" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E94" s="22" t="s">
+      <c r="E94" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F94" s="17" t="s">
@@ -5502,7 +5496,7 @@
       <c r="G94" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H94" s="26" t="s">
+      <c r="H94" s="25" t="s">
         <v>166</v>
       </c>
       <c r="I94" s="6"/>
@@ -5534,7 +5528,7 @@
       <c r="D95" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E95" s="22" t="s">
+      <c r="E95" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F95" s="17" t="s">
@@ -5543,7 +5537,7 @@
       <c r="G95" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H95" s="27" t="s">
+      <c r="H95" s="26" t="s">
         <v>168</v>
       </c>
       <c r="I95" s="6"/>
@@ -5575,7 +5569,7 @@
       <c r="D96" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E96" s="22" t="s">
+      <c r="E96" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F96" s="17" t="s">
@@ -5584,7 +5578,7 @@
       <c r="G96" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H96" s="26" t="s">
+      <c r="H96" s="25" t="s">
         <v>170</v>
       </c>
       <c r="I96" s="6"/>
@@ -5616,14 +5610,14 @@
       <c r="D97" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E97" s="22" t="s">
+      <c r="E97" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F97" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G97" s="6"/>
-      <c r="H97" s="26" t="s">
+      <c r="H97" s="25" t="s">
         <v>172</v>
       </c>
       <c r="I97" s="6"/>
@@ -5655,7 +5649,7 @@
       <c r="D98" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E98" s="22" t="s">
+      <c r="E98" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F98" s="17" t="s">
@@ -5664,7 +5658,7 @@
       <c r="G98" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H98" s="26" t="s">
+      <c r="H98" s="25" t="s">
         <v>174</v>
       </c>
       <c r="I98" s="6"/>
@@ -5696,7 +5690,7 @@
       <c r="D99" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E99" s="22" t="s">
+      <c r="E99" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F99" s="19" t="s">
@@ -5705,7 +5699,7 @@
       <c r="G99" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H99" s="27" t="s">
+      <c r="H99" s="26" t="s">
         <v>176</v>
       </c>
       <c r="I99" s="6"/>
@@ -5781,7 +5775,7 @@
       <c r="Y101" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
-      <c r="A102" s="28" t="s">
+      <c r="A102" s="27" t="s">
         <v>177</v>
       </c>
       <c r="B102" s="6" t="s">
@@ -5793,16 +5787,16 @@
       <c r="D102" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E102" s="22" t="s">
+      <c r="E102" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F102" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G102" s="23" t="s">
+      <c r="G102" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H102" s="27" t="s">
+      <c r="H102" s="26" t="s">
         <v>179</v>
       </c>
       <c r="I102" s="6"/>
@@ -5834,7 +5828,7 @@
       <c r="D103" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E103" s="22" t="s">
+      <c r="E103" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F103" s="15" t="s">
@@ -5843,7 +5837,7 @@
       <c r="G103" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H103" s="27" t="s">
+      <c r="H103" s="26" t="s">
         <v>181</v>
       </c>
       <c r="I103" s="6"/>
@@ -5875,7 +5869,7 @@
       <c r="D104" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E104" s="22" t="s">
+      <c r="E104" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F104" s="15" t="s">
@@ -5884,7 +5878,7 @@
       <c r="G104" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H104" s="27" t="s">
+      <c r="H104" s="26" t="s">
         <v>183</v>
       </c>
       <c r="I104" s="6"/>
@@ -5916,14 +5910,14 @@
       <c r="D105" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E105" s="22" t="s">
+      <c r="E105" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F105" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G105" s="6"/>
-      <c r="H105" s="26" t="s">
+      <c r="H105" s="25" t="s">
         <v>185</v>
       </c>
       <c r="I105" s="6"/>
@@ -5955,7 +5949,7 @@
       <c r="D106" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E106" s="22" t="s">
+      <c r="E106" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F106" s="15" t="s">
@@ -5964,7 +5958,7 @@
       <c r="G106" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="H106" s="27" t="s">
+      <c r="H106" s="26" t="s">
         <v>188</v>
       </c>
       <c r="I106" s="6"/>
@@ -5996,7 +5990,7 @@
       <c r="D107" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E107" s="22" t="s">
+      <c r="E107" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F107" s="15" t="s">
@@ -6005,7 +5999,7 @@
       <c r="G107" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H107" s="26" t="s">
+      <c r="H107" s="25" t="s">
         <v>190</v>
       </c>
       <c r="I107" s="6"/>
@@ -6037,7 +6031,7 @@
       <c r="D108" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E108" s="22" t="s">
+      <c r="E108" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F108" s="15" t="s">
@@ -6046,7 +6040,7 @@
       <c r="G108" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H108" s="27" t="s">
+      <c r="H108" s="26" t="s">
         <v>192</v>
       </c>
       <c r="I108" s="6"/>
@@ -6078,7 +6072,7 @@
       <c r="D109" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E109" s="22" t="s">
+      <c r="E109" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F109" s="15" t="s">
@@ -6087,7 +6081,7 @@
       <c r="G109" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H109" s="27" t="s">
+      <c r="H109" s="26" t="s">
         <v>194</v>
       </c>
       <c r="I109" s="6"/>
@@ -6119,14 +6113,14 @@
       <c r="D110" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E110" s="22" t="s">
+      <c r="E110" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F110" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G110" s="6"/>
-      <c r="H110" s="26" t="s">
+      <c r="H110" s="25" t="s">
         <v>196</v>
       </c>
       <c r="I110" s="6"/>
@@ -6158,7 +6152,7 @@
       <c r="D111" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E111" s="22" t="s">
+      <c r="E111" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F111" s="15" t="s">
@@ -6167,7 +6161,7 @@
       <c r="G111" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H111" s="26" t="s">
+      <c r="H111" s="25" t="s">
         <v>198</v>
       </c>
       <c r="I111" s="6"/>
@@ -6199,14 +6193,14 @@
       <c r="D112" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E112" s="22" t="s">
+      <c r="E112" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F112" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G112" s="6"/>
-      <c r="H112" s="26" t="s">
+      <c r="H112" s="25" t="s">
         <v>200</v>
       </c>
       <c r="I112" s="6"/>
@@ -6238,7 +6232,7 @@
       <c r="D113" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E113" s="22" t="s">
+      <c r="E113" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F113" s="17" t="s">
@@ -6247,7 +6241,7 @@
       <c r="G113" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H113" s="26" t="s">
+      <c r="H113" s="25" t="s">
         <v>202</v>
       </c>
       <c r="I113" s="6"/>
@@ -6279,14 +6273,14 @@
       <c r="D114" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E114" s="22" t="s">
+      <c r="E114" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F114" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G114" s="6"/>
-      <c r="H114" s="26" t="s">
+      <c r="H114" s="25" t="s">
         <v>204</v>
       </c>
       <c r="I114" s="6"/>
@@ -6318,14 +6312,14 @@
       <c r="D115" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E115" s="22" t="s">
+      <c r="E115" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F115" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G115" s="6"/>
-      <c r="H115" s="26" t="s">
+      <c r="H115" s="25" t="s">
         <v>206</v>
       </c>
       <c r="I115" s="6"/>
@@ -6357,7 +6351,7 @@
       <c r="D116" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E116" s="22" t="s">
+      <c r="E116" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F116" s="17" t="s">
@@ -6366,7 +6360,7 @@
       <c r="G116" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H116" s="26" t="s">
+      <c r="H116" s="25" t="s">
         <v>208</v>
       </c>
       <c r="I116" s="6"/>
@@ -6398,7 +6392,7 @@
       <c r="D117" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E117" s="22" t="s">
+      <c r="E117" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F117" s="17" t="s">
@@ -6407,7 +6401,7 @@
       <c r="G117" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H117" s="26" t="s">
+      <c r="H117" s="25" t="s">
         <v>210</v>
       </c>
       <c r="I117" s="6"/>
@@ -6439,7 +6433,7 @@
       <c r="D118" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E118" s="22" t="s">
+      <c r="E118" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F118" s="17" t="s">
@@ -6448,7 +6442,7 @@
       <c r="G118" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H118" s="26" t="s">
+      <c r="H118" s="25" t="s">
         <v>212</v>
       </c>
       <c r="I118" s="6"/>
@@ -6480,7 +6474,7 @@
       <c r="D119" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E119" s="22" t="s">
+      <c r="E119" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F119" s="17" t="s">
@@ -6489,7 +6483,7 @@
       <c r="G119" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H119" s="26" t="s">
+      <c r="H119" s="25" t="s">
         <v>214</v>
       </c>
       <c r="I119" s="6"/>
@@ -6521,14 +6515,14 @@
       <c r="D120" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E120" s="22" t="s">
+      <c r="E120" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F120" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G120" s="6"/>
-      <c r="H120" s="27" t="s">
+      <c r="H120" s="26" t="s">
         <v>216</v>
       </c>
       <c r="I120" s="6"/>
@@ -6560,7 +6554,7 @@
       <c r="D121" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E121" s="22" t="s">
+      <c r="E121" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F121" s="17" t="s">
@@ -6569,7 +6563,7 @@
       <c r="G121" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H121" s="27" t="s">
+      <c r="H121" s="26" t="s">
         <v>218</v>
       </c>
       <c r="I121" s="6"/>
@@ -6601,7 +6595,7 @@
       <c r="D122" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E122" s="22" t="s">
+      <c r="E122" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F122" s="17" t="s">
@@ -6610,7 +6604,7 @@
       <c r="G122" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H122" s="27" t="s">
+      <c r="H122" s="26" t="s">
         <v>220</v>
       </c>
       <c r="I122" s="6"/>
@@ -6642,14 +6636,14 @@
       <c r="D123" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E123" s="22" t="s">
+      <c r="E123" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F123" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G123" s="6"/>
-      <c r="H123" s="26" t="s">
+      <c r="H123" s="25" t="s">
         <v>222</v>
       </c>
       <c r="I123" s="6"/>
@@ -6681,14 +6675,14 @@
       <c r="D124" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E124" s="22" t="s">
+      <c r="E124" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F124" s="19" t="s">
         <v>63</v>
       </c>
       <c r="G124" s="6"/>
-      <c r="H124" s="26" t="s">
+      <c r="H124" s="25" t="s">
         <v>224</v>
       </c>
       <c r="I124" s="6"/>
@@ -6720,14 +6714,14 @@
       <c r="D125" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E125" s="22" t="s">
+      <c r="E125" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F125" s="19" t="s">
         <v>63</v>
       </c>
       <c r="G125" s="6"/>
-      <c r="H125" s="26" t="s">
+      <c r="H125" s="25" t="s">
         <v>226</v>
       </c>
       <c r="I125" s="6"/>
@@ -6803,7 +6797,7 @@
       <c r="Y127" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25">
-      <c r="A128" s="28" t="s">
+      <c r="A128" s="27" t="s">
         <v>227</v>
       </c>
       <c r="B128" s="6" t="s">
@@ -6822,7 +6816,7 @@
         <v>14</v>
       </c>
       <c r="G128" s="6"/>
-      <c r="H128" s="26" t="s">
+      <c r="H128" s="25" t="s">
         <v>229</v>
       </c>
       <c r="I128" s="6"/>
@@ -6863,7 +6857,7 @@
       <c r="G129" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H129" s="27" t="s">
+      <c r="H129" s="26" t="s">
         <v>231</v>
       </c>
       <c r="I129" s="6"/>
@@ -6904,7 +6898,7 @@
       <c r="G130" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H130" s="26" t="s">
+      <c r="H130" s="25" t="s">
         <v>233</v>
       </c>
       <c r="I130" s="6"/>
@@ -6945,7 +6939,7 @@
       <c r="G131" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H131" s="26" t="s">
+      <c r="H131" s="25" t="s">
         <v>235</v>
       </c>
       <c r="I131" s="6"/>
@@ -6986,7 +6980,7 @@
       <c r="G132" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H132" s="26" t="s">
+      <c r="H132" s="25" t="s">
         <v>237</v>
       </c>
       <c r="I132" s="6"/>
@@ -7027,7 +7021,7 @@
       <c r="G133" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H133" s="27" t="s">
+      <c r="H133" s="26" t="s">
         <v>239</v>
       </c>
       <c r="I133" s="6"/>
@@ -7068,7 +7062,7 @@
       <c r="G134" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H134" s="27" t="s">
+      <c r="H134" s="26" t="s">
         <v>241</v>
       </c>
       <c r="I134" s="6"/>
@@ -7109,7 +7103,7 @@
       <c r="G135" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H135" s="26" t="s">
+      <c r="H135" s="25" t="s">
         <v>243</v>
       </c>
       <c r="I135" s="6"/>
@@ -7150,7 +7144,7 @@
       <c r="G136" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H136" s="27" t="s">
+      <c r="H136" s="26" t="s">
         <v>245</v>
       </c>
       <c r="I136" s="6"/>
@@ -7189,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="G137" s="6"/>
-      <c r="H137" s="26" t="s">
+      <c r="H137" s="25" t="s">
         <v>247</v>
       </c>
       <c r="I137" s="6"/>
@@ -7230,7 +7224,7 @@
       <c r="G138" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H138" s="26" t="s">
+      <c r="H138" s="25" t="s">
         <v>249</v>
       </c>
       <c r="I138" s="6"/>
@@ -7271,7 +7265,7 @@
       <c r="G139" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H139" s="26" t="s">
+      <c r="H139" s="25" t="s">
         <v>251</v>
       </c>
       <c r="I139" s="6"/>
@@ -7312,7 +7306,7 @@
       <c r="G140" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H140" s="27" t="s">
+      <c r="H140" s="26" t="s">
         <v>253</v>
       </c>
       <c r="I140" s="6"/>
@@ -7351,7 +7345,7 @@
         <v>63</v>
       </c>
       <c r="G141" s="6"/>
-      <c r="H141" s="27" t="s">
+      <c r="H141" s="26" t="s">
         <v>255</v>
       </c>
       <c r="I141" s="6"/>
@@ -7392,7 +7386,7 @@
       <c r="G142" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H142" s="26" t="s">
+      <c r="H142" s="25" t="s">
         <v>257</v>
       </c>
       <c r="I142" s="6"/>
@@ -7468,7 +7462,7 @@
       <c r="Y144" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
-      <c r="A145" s="28" t="s">
+      <c r="A145" s="27" t="s">
         <v>258</v>
       </c>
       <c r="B145" s="6" t="s">
@@ -7480,14 +7474,14 @@
       <c r="D145" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E145" s="29" t="s">
+      <c r="E145" s="28" t="s">
         <v>260</v>
       </c>
       <c r="F145" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G145" s="6"/>
-      <c r="H145" s="26" t="s">
+      <c r="H145" s="25" t="s">
         <v>261</v>
       </c>
       <c r="I145" s="6"/>
@@ -7519,14 +7513,14 @@
       <c r="D146" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="E146" s="29" t="s">
+      <c r="E146" s="28" t="s">
         <v>263</v>
       </c>
       <c r="F146" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G146" s="6"/>
-      <c r="H146" s="26" t="s">
+      <c r="H146" s="25" t="s">
         <v>264</v>
       </c>
       <c r="I146" s="6"/>
@@ -7558,14 +7552,14 @@
       <c r="D147" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E147" s="29" t="s">
+      <c r="E147" s="28" t="s">
         <v>266</v>
       </c>
       <c r="F147" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G147" s="6"/>
-      <c r="H147" s="26" t="s">
+      <c r="H147" s="25" t="s">
         <v>267</v>
       </c>
       <c r="I147" s="6"/>
@@ -7597,14 +7591,14 @@
       <c r="D148" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E148" s="29" t="s">
+      <c r="E148" s="28" t="s">
         <v>269</v>
       </c>
       <c r="F148" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G148" s="6"/>
-      <c r="H148" s="26" t="s">
+      <c r="H148" s="25" t="s">
         <v>270</v>
       </c>
       <c r="I148" s="6"/>
@@ -7636,14 +7630,14 @@
       <c r="D149" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E149" s="29" t="s">
+      <c r="E149" s="28" t="s">
         <v>272</v>
       </c>
       <c r="F149" s="19" t="s">
         <v>63</v>
       </c>
       <c r="G149" s="6"/>
-      <c r="H149" s="26" t="s">
+      <c r="H149" s="25" t="s">
         <v>273</v>
       </c>
       <c r="I149" s="6"/>
@@ -7675,14 +7669,14 @@
       <c r="D150" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E150" s="29" t="s">
+      <c r="E150" s="28" t="s">
         <v>275</v>
       </c>
       <c r="F150" s="19" t="s">
         <v>63</v>
       </c>
       <c r="G150" s="6"/>
-      <c r="H150" s="27" t="s">
+      <c r="H150" s="26" t="s">
         <v>276</v>
       </c>
       <c r="I150" s="6"/>
@@ -7758,7 +7752,7 @@
       <c r="Y152" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25">
-      <c r="A153" s="28" t="s">
+      <c r="A153" s="27" t="s">
         <v>277</v>
       </c>
       <c r="B153" s="6" t="s">
@@ -7770,14 +7764,14 @@
       <c r="D153" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E153" s="29" t="s">
+      <c r="E153" s="28" t="s">
         <v>278</v>
       </c>
       <c r="F153" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G153" s="6"/>
-      <c r="H153" s="26" t="s">
+      <c r="H153" s="25" t="s">
         <v>279</v>
       </c>
       <c r="I153" s="6"/>
@@ -7809,14 +7803,14 @@
       <c r="D154" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E154" s="29" t="s">
+      <c r="E154" s="28" t="s">
         <v>281</v>
       </c>
       <c r="F154" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G154" s="6"/>
-      <c r="H154" s="26" t="s">
+      <c r="H154" s="25" t="s">
         <v>282</v>
       </c>
       <c r="I154" s="6"/>
@@ -7848,14 +7842,14 @@
       <c r="D155" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E155" s="29" t="s">
+      <c r="E155" s="28" t="s">
         <v>284</v>
       </c>
       <c r="F155" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G155" s="6"/>
-      <c r="H155" s="27" t="s">
+      <c r="H155" s="26" t="s">
         <v>285</v>
       </c>
       <c r="I155" s="6"/>
@@ -7887,14 +7881,14 @@
       <c r="D156" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E156" s="29" t="s">
+      <c r="E156" s="28" t="s">
         <v>287</v>
       </c>
       <c r="F156" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G156" s="6"/>
-      <c r="H156" s="26" t="s">
+      <c r="H156" s="25" t="s">
         <v>288</v>
       </c>
       <c r="I156" s="6"/>
@@ -7926,14 +7920,14 @@
       <c r="D157" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E157" s="29" t="s">
+      <c r="E157" s="28" t="s">
         <v>290</v>
       </c>
       <c r="F157" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G157" s="6"/>
-      <c r="H157" s="27" t="s">
+      <c r="H157" s="26" t="s">
         <v>285</v>
       </c>
       <c r="I157" s="6"/>
@@ -7955,7 +7949,7 @@
       <c r="Y157" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25">
-      <c r="A158" s="30"/>
+      <c r="A158" s="29"/>
       <c r="B158" s="1"/>
       <c r="C158" s="2"/>
       <c r="D158" s="1"/>
@@ -8009,7 +8003,7 @@
       <c r="Y159" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
-      <c r="A160" s="28" t="s">
+      <c r="A160" s="27" t="s">
         <v>291</v>
       </c>
       <c r="B160" s="6" t="s">
@@ -8021,14 +8015,14 @@
       <c r="D160" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E160" s="29" t="s">
+      <c r="E160" s="28" t="s">
         <v>293</v>
       </c>
       <c r="F160" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G160" s="6"/>
-      <c r="H160" s="26" t="s">
+      <c r="H160" s="25" t="s">
         <v>294</v>
       </c>
       <c r="I160" s="6"/>
@@ -8060,7 +8054,7 @@
       <c r="D161" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E161" s="31" t="s">
+      <c r="E161" s="30" t="s">
         <v>296</v>
       </c>
       <c r="F161" s="17" t="s">
@@ -8069,7 +8063,7 @@
       <c r="G161" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H161" s="26" t="s">
+      <c r="H161" s="25" t="s">
         <v>297</v>
       </c>
       <c r="I161" s="6"/>
@@ -8101,7 +8095,7 @@
       <c r="D162" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E162" s="31" t="s">
+      <c r="E162" s="30" t="s">
         <v>296</v>
       </c>
       <c r="F162" s="17" t="s">
@@ -8110,7 +8104,7 @@
       <c r="G162" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H162" s="26" t="s">
+      <c r="H162" s="25" t="s">
         <v>299</v>
       </c>
       <c r="I162" s="6"/>
@@ -8142,14 +8136,14 @@
       <c r="D163" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="E163" s="29" t="s">
+      <c r="E163" s="28" t="s">
         <v>301</v>
       </c>
       <c r="F163" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G163" s="6"/>
-      <c r="H163" s="26" t="s">
+      <c r="H163" s="25" t="s">
         <v>299</v>
       </c>
       <c r="I163" s="6"/>
@@ -8181,14 +8175,14 @@
       <c r="D164" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E164" s="29" t="s">
+      <c r="E164" s="28" t="s">
         <v>301</v>
       </c>
       <c r="F164" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G164" s="6"/>
-      <c r="H164" s="26" t="s">
+      <c r="H164" s="25" t="s">
         <v>303</v>
       </c>
       <c r="I164" s="6"/>
@@ -8220,14 +8214,14 @@
       <c r="D165" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E165" s="29" t="s">
+      <c r="E165" s="28" t="s">
         <v>305</v>
       </c>
       <c r="F165" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G165" s="6"/>
-      <c r="H165" s="26" t="s">
+      <c r="H165" s="25" t="s">
         <v>306</v>
       </c>
       <c r="I165" s="6"/>
@@ -8259,14 +8253,14 @@
       <c r="D166" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E166" s="29" t="s">
+      <c r="E166" s="28" t="s">
         <v>305</v>
       </c>
       <c r="F166" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G166" s="6"/>
-      <c r="H166" s="26" t="s">
+      <c r="H166" s="25" t="s">
         <v>308</v>
       </c>
       <c r="I166" s="6"/>
@@ -8298,14 +8292,14 @@
       <c r="D167" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E167" s="29" t="s">
+      <c r="E167" s="28" t="s">
         <v>310</v>
       </c>
       <c r="F167" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G167" s="6"/>
-      <c r="H167" s="26" t="s">
+      <c r="H167" s="25" t="s">
         <v>311</v>
       </c>
       <c r="I167" s="6"/>
@@ -8337,14 +8331,14 @@
       <c r="D168" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="E168" s="29" t="s">
+      <c r="E168" s="28" t="s">
         <v>313</v>
       </c>
       <c r="F168" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G168" s="6"/>
-      <c r="H168" s="26" t="s">
+      <c r="H168" s="25" t="s">
         <v>314</v>
       </c>
       <c r="I168" s="6"/>
@@ -8376,14 +8370,14 @@
       <c r="D169" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E169" s="29" t="s">
+      <c r="E169" s="28" t="s">
         <v>316</v>
       </c>
       <c r="F169" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G169" s="6"/>
-      <c r="H169" s="27" t="s">
+      <c r="H169" s="26" t="s">
         <v>317</v>
       </c>
       <c r="I169" s="6"/>
@@ -8415,14 +8409,14 @@
       <c r="D170" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E170" s="29" t="s">
+      <c r="E170" s="28" t="s">
         <v>319</v>
       </c>
       <c r="F170" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G170" s="6"/>
-      <c r="H170" s="26" t="s">
+      <c r="H170" s="25" t="s">
         <v>320</v>
       </c>
       <c r="I170" s="6"/>
@@ -8454,14 +8448,14 @@
       <c r="D171" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="E171" s="29" t="s">
+      <c r="E171" s="28" t="s">
         <v>322</v>
       </c>
       <c r="F171" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G171" s="6"/>
-      <c r="H171" s="26" t="s">
+      <c r="H171" s="25" t="s">
         <v>323</v>
       </c>
       <c r="I171" s="6"/>
@@ -8493,14 +8487,14 @@
       <c r="D172" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E172" s="29" t="s">
+      <c r="E172" s="28" t="s">
         <v>325</v>
       </c>
       <c r="F172" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G172" s="6"/>
-      <c r="H172" s="26" t="s">
+      <c r="H172" s="25" t="s">
         <v>326</v>
       </c>
       <c r="I172" s="6"/>
@@ -8532,14 +8526,14 @@
       <c r="D173" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="E173" s="29" t="s">
+      <c r="E173" s="28" t="s">
         <v>328</v>
       </c>
       <c r="F173" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G173" s="6"/>
-      <c r="H173" s="26" t="s">
+      <c r="H173" s="25" t="s">
         <v>329</v>
       </c>
       <c r="I173" s="6"/>
@@ -8571,14 +8565,14 @@
       <c r="D174" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E174" s="29" t="s">
+      <c r="E174" s="28" t="s">
         <v>330</v>
       </c>
       <c r="F174" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G174" s="6"/>
-      <c r="H174" s="26" t="s">
+      <c r="H174" s="25" t="s">
         <v>331</v>
       </c>
       <c r="I174" s="6"/>
@@ -8610,14 +8604,14 @@
       <c r="D175" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="E175" s="29" t="s">
+      <c r="E175" s="28" t="s">
         <v>333</v>
       </c>
       <c r="F175" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G175" s="6"/>
-      <c r="H175" s="26" t="s">
+      <c r="H175" s="25" t="s">
         <v>334</v>
       </c>
       <c r="I175" s="6"/>
@@ -8649,14 +8643,14 @@
       <c r="D176" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E176" s="29" t="s">
+      <c r="E176" s="28" t="s">
         <v>336</v>
       </c>
       <c r="F176" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G176" s="6"/>
-      <c r="H176" s="26" t="s">
+      <c r="H176" s="25" t="s">
         <v>337</v>
       </c>
       <c r="I176" s="6"/>
@@ -8688,14 +8682,14 @@
       <c r="D177" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E177" s="29" t="s">
+      <c r="E177" s="28" t="s">
         <v>339</v>
       </c>
       <c r="F177" s="19" t="s">
         <v>63</v>
       </c>
       <c r="G177" s="6"/>
-      <c r="H177" s="27" t="s">
+      <c r="H177" s="26" t="s">
         <v>340</v>
       </c>
       <c r="I177" s="6"/>
@@ -8727,14 +8721,14 @@
       <c r="D178" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="E178" s="29" t="s">
+      <c r="E178" s="28" t="s">
         <v>342</v>
       </c>
       <c r="F178" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G178" s="6"/>
-      <c r="H178" s="26" t="s">
+      <c r="H178" s="25" t="s">
         <v>343</v>
       </c>
       <c r="I178" s="6"/>
@@ -8766,14 +8760,14 @@
       <c r="D179" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E179" s="29" t="s">
+      <c r="E179" s="28" t="s">
         <v>296</v>
       </c>
       <c r="F179" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G179" s="6"/>
-      <c r="H179" s="26" t="s">
+      <c r="H179" s="25" t="s">
         <v>345</v>
       </c>
       <c r="I179" s="6"/>
@@ -8805,14 +8799,14 @@
       <c r="D180" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E180" s="29" t="s">
+      <c r="E180" s="28" t="s">
         <v>347</v>
       </c>
       <c r="F180" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G180" s="6"/>
-      <c r="H180" s="26" t="s">
+      <c r="H180" s="25" t="s">
         <v>348</v>
       </c>
       <c r="I180" s="6"/>
@@ -8844,14 +8838,14 @@
       <c r="D181" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="E181" s="29" t="s">
+      <c r="E181" s="28" t="s">
         <v>350</v>
       </c>
       <c r="F181" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G181" s="6"/>
-      <c r="H181" s="26" t="s">
+      <c r="H181" s="25" t="s">
         <v>351</v>
       </c>
       <c r="I181" s="6"/>
@@ -8883,14 +8877,14 @@
       <c r="D182" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E182" s="29" t="s">
+      <c r="E182" s="28" t="s">
         <v>353</v>
       </c>
       <c r="F182" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G182" s="6"/>
-      <c r="H182" s="27" t="s">
+      <c r="H182" s="26" t="s">
         <v>354</v>
       </c>
       <c r="I182" s="6"/>
@@ -8922,14 +8916,14 @@
       <c r="D183" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="E183" s="29" t="s">
+      <c r="E183" s="28" t="s">
         <v>356</v>
       </c>
       <c r="F183" s="19" t="s">
         <v>63</v>
       </c>
       <c r="G183" s="6"/>
-      <c r="H183" s="27" t="s">
+      <c r="H183" s="26" t="s">
         <v>357</v>
       </c>
       <c r="I183" s="6"/>
@@ -8961,14 +8955,14 @@
       <c r="D184" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="E184" s="29" t="s">
+      <c r="E184" s="28" t="s">
         <v>359</v>
       </c>
       <c r="F184" s="19" t="s">
         <v>63</v>
       </c>
       <c r="G184" s="6"/>
-      <c r="H184" s="27" t="s">
+      <c r="H184" s="26" t="s">
         <v>360</v>
       </c>
       <c r="I184" s="6"/>
@@ -9000,14 +8994,14 @@
       <c r="D185" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="E185" s="29" t="s">
+      <c r="E185" s="28" t="s">
         <v>313</v>
       </c>
       <c r="F185" s="19" t="s">
         <v>63</v>
       </c>
       <c r="G185" s="6"/>
-      <c r="H185" s="26" t="s">
+      <c r="H185" s="25" t="s">
         <v>362</v>
       </c>
       <c r="I185" s="6"/>
@@ -9083,7 +9077,7 @@
       <c r="Y187" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="17.25">
-      <c r="A188" s="28" t="s">
+      <c r="A188" s="27" t="s">
         <v>363</v>
       </c>
       <c r="B188" s="6" t="s">
@@ -9102,7 +9096,7 @@
         <v>14</v>
       </c>
       <c r="G188" s="6"/>
-      <c r="H188" s="26" t="s">
+      <c r="H188" s="25" t="s">
         <v>365</v>
       </c>
       <c r="I188" s="6"/>
@@ -9141,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="G189" s="6"/>
-      <c r="H189" s="26" t="s">
+      <c r="H189" s="25" t="s">
         <v>367</v>
       </c>
       <c r="I189" s="6"/>
@@ -9180,7 +9174,7 @@
         <v>27</v>
       </c>
       <c r="G190" s="6"/>
-      <c r="H190" s="27" t="s">
+      <c r="H190" s="26" t="s">
         <v>369</v>
       </c>
       <c r="I190" s="6"/>
@@ -9219,7 +9213,7 @@
         <v>27</v>
       </c>
       <c r="G191" s="6"/>
-      <c r="H191" s="27" t="s">
+      <c r="H191" s="26" t="s">
         <v>371</v>
       </c>
       <c r="I191" s="6"/>
@@ -9258,7 +9252,7 @@
         <v>27</v>
       </c>
       <c r="G192" s="6"/>
-      <c r="H192" s="26" t="s">
+      <c r="H192" s="25" t="s">
         <v>373</v>
       </c>
       <c r="I192" s="6"/>
@@ -9297,7 +9291,7 @@
         <v>27</v>
       </c>
       <c r="G193" s="6"/>
-      <c r="H193" s="26" t="s">
+      <c r="H193" s="25" t="s">
         <v>375</v>
       </c>
       <c r="I193" s="6"/>
@@ -9336,7 +9330,7 @@
         <v>27</v>
       </c>
       <c r="G194" s="6"/>
-      <c r="H194" s="26" t="s">
+      <c r="H194" s="25" t="s">
         <v>377</v>
       </c>
       <c r="I194" s="6"/>
@@ -9375,7 +9369,7 @@
         <v>27</v>
       </c>
       <c r="G195" s="6"/>
-      <c r="H195" s="27" t="s">
+      <c r="H195" s="26" t="s">
         <v>379</v>
       </c>
       <c r="I195" s="6"/>
@@ -9414,7 +9408,7 @@
         <v>27</v>
       </c>
       <c r="G196" s="6"/>
-      <c r="H196" s="26" t="s">
+      <c r="H196" s="25" t="s">
         <v>381</v>
       </c>
       <c r="I196" s="6"/>
@@ -9453,7 +9447,7 @@
         <v>27</v>
       </c>
       <c r="G197" s="6"/>
-      <c r="H197" s="26" t="s">
+      <c r="H197" s="25" t="s">
         <v>383</v>
       </c>
       <c r="I197" s="6"/>
@@ -9492,7 +9486,7 @@
         <v>27</v>
       </c>
       <c r="G198" s="6"/>
-      <c r="H198" s="27" t="s">
+      <c r="H198" s="26" t="s">
         <v>385</v>
       </c>
       <c r="I198" s="6"/>
@@ -9531,7 +9525,7 @@
         <v>27</v>
       </c>
       <c r="G199" s="6"/>
-      <c r="H199" s="26" t="s">
+      <c r="H199" s="25" t="s">
         <v>387</v>
       </c>
       <c r="I199" s="6"/>
@@ -9570,7 +9564,7 @@
         <v>27</v>
       </c>
       <c r="G200" s="6"/>
-      <c r="H200" s="26" t="s">
+      <c r="H200" s="25" t="s">
         <v>389</v>
       </c>
       <c r="I200" s="6"/>
@@ -9609,7 +9603,7 @@
         <v>27</v>
       </c>
       <c r="G201" s="6"/>
-      <c r="H201" s="26" t="s">
+      <c r="H201" s="25" t="s">
         <v>391</v>
       </c>
       <c r="I201" s="6"/>
@@ -9648,7 +9642,7 @@
         <v>27</v>
       </c>
       <c r="G202" s="6"/>
-      <c r="H202" s="27" t="s">
+      <c r="H202" s="26" t="s">
         <v>393</v>
       </c>
       <c r="I202" s="6"/>
@@ -9687,7 +9681,7 @@
         <v>63</v>
       </c>
       <c r="G203" s="6"/>
-      <c r="H203" s="27" t="s">
+      <c r="H203" s="26" t="s">
         <v>395</v>
       </c>
       <c r="I203" s="6"/>
@@ -9726,7 +9720,7 @@
         <v>63</v>
       </c>
       <c r="G204" s="6"/>
-      <c r="H204" s="27" t="s">
+      <c r="H204" s="26" t="s">
         <v>397</v>
       </c>
       <c r="I204" s="6"/>
@@ -9765,7 +9759,7 @@
         <v>63</v>
       </c>
       <c r="G205" s="6"/>
-      <c r="H205" s="27" t="s">
+      <c r="H205" s="26" t="s">
         <v>399</v>
       </c>
       <c r="I205" s="6"/>
@@ -9804,7 +9798,7 @@
         <v>63</v>
       </c>
       <c r="G206" s="6"/>
-      <c r="H206" s="26" t="s">
+      <c r="H206" s="25" t="s">
         <v>401</v>
       </c>
       <c r="I206" s="6"/>
@@ -9843,7 +9837,7 @@
         <v>63</v>
       </c>
       <c r="G207" s="6"/>
-      <c r="H207" s="26" t="s">
+      <c r="H207" s="25" t="s">
         <v>403</v>
       </c>
       <c r="I207" s="6"/>
@@ -9882,7 +9876,7 @@
         <v>63</v>
       </c>
       <c r="G208" s="6"/>
-      <c r="H208" s="27" t="s">
+      <c r="H208" s="26" t="s">
         <v>405</v>
       </c>
       <c r="I208" s="6"/>
@@ -9958,7 +9952,7 @@
       <c r="Y210" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25">
-      <c r="A211" s="28" t="s">
+      <c r="A211" s="27" t="s">
         <v>406</v>
       </c>
       <c r="B211" s="6" t="s">
@@ -9977,7 +9971,7 @@
         <v>14</v>
       </c>
       <c r="G211" s="6"/>
-      <c r="H211" s="27" t="s">
+      <c r="H211" s="26" t="s">
         <v>408</v>
       </c>
       <c r="I211" s="6"/>
@@ -10016,7 +10010,7 @@
         <v>27</v>
       </c>
       <c r="G212" s="6"/>
-      <c r="H212" s="26" t="s">
+      <c r="H212" s="25" t="s">
         <v>410</v>
       </c>
       <c r="I212" s="6"/>
@@ -10055,7 +10049,7 @@
         <v>27</v>
       </c>
       <c r="G213" s="6"/>
-      <c r="H213" s="26" t="s">
+      <c r="H213" s="25" t="s">
         <v>412</v>
       </c>
       <c r="I213" s="6"/>
@@ -10094,7 +10088,7 @@
         <v>27</v>
       </c>
       <c r="G214" s="6"/>
-      <c r="H214" s="26" t="s">
+      <c r="H214" s="25" t="s">
         <v>414</v>
       </c>
       <c r="I214" s="6"/>
@@ -10133,7 +10127,7 @@
         <v>27</v>
       </c>
       <c r="G215" s="6"/>
-      <c r="H215" s="26" t="s">
+      <c r="H215" s="25" t="s">
         <v>416</v>
       </c>
       <c r="I215" s="6"/>
@@ -10172,7 +10166,7 @@
         <v>63</v>
       </c>
       <c r="G216" s="6"/>
-      <c r="H216" s="26" t="s">
+      <c r="H216" s="25" t="s">
         <v>418</v>
       </c>
       <c r="I216" s="6"/>

--- a/ProductFaangCodingPractice/ProblemSolvingList_ONLY_FOCUS.xlsx
+++ b/ProductFaangCodingPractice/ProblemSolvingList_ONLY_FOCUS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="421">
   <si>
     <t>Do NOT send any edit request to this sheet. Instead, make a copy of your own.</t>
   </si>
@@ -72,51 +72,54 @@
     <t>ARRAYS</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Majority Element</t>
+  </si>
+  <si>
+    <t>Problem Link</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>Solution Link</t>
+  </si>
+  <si>
+    <t>Amazon Google</t>
+  </si>
+  <si>
+    <t>Repeat &amp; missing number</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Hashing</t>
+  </si>
+  <si>
+    <t>Merge 2 sorted array without xtra space</t>
+  </si>
+  <si>
+    <t>Amdocs Brocade Goldman Sachs Juniper Networks Linkedin Microsoft Quikr Snapdeal Synopsys Zoho Adobe</t>
+  </si>
+  <si>
+    <t>Sorting</t>
+  </si>
+  <si>
+    <t>Single Number</t>
+  </si>
+  <si>
+    <t>Stock Buy &amp; Sell</t>
+  </si>
+  <si>
+    <t>Amazon DEShaw Directi Flipkart Goldman Sachs Intuit MakeMyTrip Microsoft Ola Cabs Oracle Paytm Pubmatic Quikr Salesforce Sapient Swiggy Walmart Media.net Google</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
-    <t>Majority Element</t>
-  </si>
-  <si>
-    <t>Problem Link</t>
-  </si>
-  <si>
-    <t>Easy</t>
-  </si>
-  <si>
-    <t>Solution Link</t>
-  </si>
-  <si>
-    <t>Amazon Google</t>
-  </si>
-  <si>
-    <t>Repeat &amp; missing number</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Hashing</t>
-  </si>
-  <si>
-    <t>Merge 2 sorted array without xtra space</t>
-  </si>
-  <si>
-    <t>Amdocs Brocade Goldman Sachs Juniper Networks Linkedin Microsoft Quikr Snapdeal Synopsys Zoho Adobe</t>
-  </si>
-  <si>
-    <t>Sorting</t>
-  </si>
-  <si>
-    <t>Single Number</t>
-  </si>
-  <si>
-    <t>Stock Buy &amp; Sell</t>
-  </si>
-  <si>
-    <t>Amazon DEShaw Directi Flipkart Goldman Sachs Intuit MakeMyTrip Microsoft Ola Cabs Oracle Paytm Pubmatic Quikr Salesforce Sapient Swiggy Walmart Media.net Google</t>
-  </si>
-  <si>
     <t>Kadane's Algorithm</t>
   </si>
   <si>
@@ -478,6 +481,9 @@
   </si>
   <si>
     <t>STACK &amp; QUEUE</t>
+  </si>
+  <si>
+    <t>YES</t>
   </si>
   <si>
     <t>Implement Stack using Queue</t>
@@ -1301,7 +1307,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1319,6 +1325,12 @@
       <sz val="11"/>
       <color rgb="FFffffff"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -1484,7 +1496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1498,19 +1510,19 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
@@ -1519,35 +1531,35 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1556,24 +1568,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="14" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="15" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1890,31 +1905,31 @@
   <dimension ref="A1:Y1002"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="31" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="31" width="12.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="32" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="31" width="36.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="33" width="20.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="33" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="31" width="39.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="33" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="31" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="32" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="32" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="33" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="32" width="36.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="34" width="20.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="34" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="32" width="39.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="34" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="32" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -2076,7 +2091,7 @@
       <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="2">
@@ -2085,16 +2100,16 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="17" t="s">
         <v>16</v>
       </c>
       <c r="I6" s="6"/>
@@ -2117,7 +2132,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
       <c r="A7" s="5"/>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="2">
@@ -2126,16 +2141,16 @@
       <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="17" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="6" t="s">
@@ -2160,7 +2175,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
       <c r="A8" s="5"/>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="2">
@@ -2169,16 +2184,16 @@
       <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="17" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -2203,7 +2218,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
       <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="2">
@@ -2212,16 +2227,16 @@
       <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="17"/>
       <c r="I9" s="6"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -2242,7 +2257,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
       <c r="A10" s="5"/>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="2">
@@ -2251,16 +2266,16 @@
       <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="17" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="6"/>
@@ -2289,7 +2304,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="16"/>
+      <c r="H11" s="17"/>
       <c r="I11" s="6"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -2311,25 +2326,25 @@
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2">
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="16" t="s">
-        <v>28</v>
+      <c r="H12" s="17" t="s">
+        <v>29</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="1"/>
@@ -2352,24 +2367,24 @@
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2">
         <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="14" t="s">
+      <c r="F13" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="16"/>
+      <c r="H13" s="17"/>
       <c r="I13" s="6"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -2391,25 +2406,25 @@
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2">
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="14" t="s">
+      <c r="F14" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="16" t="s">
-        <v>31</v>
+      <c r="H14" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="1"/>
@@ -2432,25 +2447,25 @@
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C15" s="2">
         <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="14" t="s">
+      <c r="F15" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="16" t="s">
-        <v>33</v>
+      <c r="H15" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>22</v>
@@ -2475,25 +2490,25 @@
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C16" s="2">
         <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="14" t="s">
+      <c r="F16" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="18" t="s">
-        <v>35</v>
+      <c r="H16" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>19</v>
@@ -2518,24 +2533,24 @@
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2">
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="14" t="s">
+      <c r="F17" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="18"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="6" t="s">
         <v>19</v>
       </c>
@@ -2559,26 +2574,26 @@
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C18" s="2">
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="14" t="s">
+      <c r="F18" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="16"/>
+      <c r="H18" s="17"/>
       <c r="I18" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -2600,25 +2615,25 @@
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C19" s="2">
         <v>13</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="14" t="s">
+      <c r="F19" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="16" t="s">
-        <v>40</v>
+      <c r="H19" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>22</v>
@@ -2643,23 +2658,23 @@
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
       <c r="A20" s="5"/>
       <c r="B20" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C20" s="2">
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="17" t="s">
-        <v>27</v>
+      <c r="F20" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G20" s="6"/>
-      <c r="H20" s="16" t="s">
-        <v>42</v>
+      <c r="H20" s="17" t="s">
+        <v>43</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>22</v>
@@ -2684,26 +2699,26 @@
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
       <c r="A21" s="5"/>
       <c r="B21" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C21" s="2">
         <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="17" t="s">
-        <v>27</v>
+      <c r="F21" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G21" s="6"/>
-      <c r="H21" s="16" t="s">
-        <v>44</v>
+      <c r="H21" s="17" t="s">
+        <v>45</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -2725,26 +2740,26 @@
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
       <c r="A22" s="5"/>
       <c r="B22" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C22" s="2">
         <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>27</v>
+      <c r="F22" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G22" s="6"/>
-      <c r="H22" s="16" t="s">
-        <v>47</v>
+      <c r="H22" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2766,26 +2781,26 @@
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C23" s="2">
         <v>17</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>27</v>
+      <c r="F23" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G23" s="6"/>
-      <c r="H23" s="16" t="s">
-        <v>50</v>
+      <c r="H23" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -2807,25 +2822,25 @@
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C24" s="2">
         <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" s="14" t="s">
+      <c r="F24" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="16" t="s">
-        <v>53</v>
+      <c r="H24" s="17" t="s">
+        <v>54</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="1"/>
@@ -2848,22 +2863,22 @@
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C25" s="2">
         <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>27</v>
+      <c r="F25" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G25" s="6"/>
-      <c r="H25" s="16"/>
+      <c r="H25" s="17"/>
       <c r="I25" s="6" t="s">
         <v>19</v>
       </c>
@@ -2887,28 +2902,28 @@
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C26" s="2">
         <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="14" t="s">
+      <c r="F26" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H26" s="16" t="s">
-        <v>56</v>
+      <c r="H26" s="17" t="s">
+        <v>57</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -2935,7 +2950,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="16"/>
+      <c r="H27" s="17"/>
       <c r="I27" s="6"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2957,26 +2972,26 @@
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C28" s="2">
         <v>21</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="19" t="s">
-        <v>59</v>
+      <c r="F28" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="G28" s="6"/>
-      <c r="H28" s="16" t="s">
-        <v>60</v>
+      <c r="H28" s="17" t="s">
+        <v>61</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2998,25 +3013,25 @@
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
       <c r="A29" s="5"/>
       <c r="B29" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C29" s="2">
         <v>22</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G29" s="14" t="s">
+      <c r="F29" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H29" s="16" t="s">
-        <v>64</v>
+      <c r="H29" s="17" t="s">
+        <v>65</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="1"/>
@@ -3039,25 +3054,25 @@
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C30" s="2">
         <v>23</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="16" t="s">
-        <v>66</v>
+      <c r="H30" s="17" t="s">
+        <v>67</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>19</v>
@@ -3082,24 +3097,24 @@
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C31" s="2">
         <v>24</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E31" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="19" t="s">
-        <v>63</v>
+      <c r="F31" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G31" s="6"/>
-      <c r="H31" s="16"/>
+      <c r="H31" s="17"/>
       <c r="I31" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -3121,24 +3136,24 @@
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
       <c r="A32" s="5"/>
       <c r="B32" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C32" s="2">
         <v>25</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E32" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" s="14" t="s">
+      <c r="F32" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="16"/>
+      <c r="H32" s="17"/>
       <c r="I32" s="6"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -3165,7 +3180,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="1"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="16"/>
+      <c r="H33" s="17"/>
       <c r="I33" s="6"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -3192,7 +3207,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="1"/>
       <c r="G34" s="6"/>
-      <c r="H34" s="16"/>
+      <c r="H34" s="17"/>
       <c r="I34" s="6"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -3212,29 +3227,29 @@
       <c r="Y34" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
-      <c r="A35" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="6" t="s">
+      <c r="A35" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G35" s="22" t="s">
+      <c r="F35" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="16" t="s">
-        <v>71</v>
+      <c r="H35" s="17" t="s">
+        <v>72</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="1"/>
@@ -3256,22 +3271,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="5"/>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="2">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G36" s="14" t="s">
+      <c r="F36" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36" s="15" t="s">
         <v>15</v>
       </c>
       <c r="H36" s="1"/>
@@ -3295,25 +3310,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="5"/>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="2">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G37" s="14" t="s">
+      <c r="F37" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H37" s="16"/>
+      <c r="H37" s="17"/>
       <c r="I37" s="6"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -3334,26 +3349,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="5"/>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="2">
         <v>4</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G38" s="14" t="s">
+      <c r="F38" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H38" s="16" t="s">
-        <v>75</v>
+      <c r="H38" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="1"/>
@@ -3375,22 +3390,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="5"/>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="2">
         <v>5</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G39" s="14" t="s">
+      <c r="F39" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="15" t="s">
         <v>15</v>
       </c>
       <c r="H39" s="1"/>
@@ -3414,26 +3429,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="2">
         <v>6</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E40" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G40" s="14" t="s">
+      <c r="F40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H40" s="16" t="s">
-        <v>78</v>
+      <c r="H40" s="17" t="s">
+        <v>79</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="1"/>
@@ -3455,24 +3470,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="5"/>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="2">
         <v>7</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E41" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="19" t="s">
-        <v>63</v>
+      <c r="F41" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G41" s="6"/>
-      <c r="H41" s="16" t="s">
-        <v>80</v>
+      <c r="H41" s="17" t="s">
+        <v>81</v>
       </c>
       <c r="I41" s="6"/>
       <c r="J41" s="1"/>
@@ -3500,7 +3515,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="1"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="16"/>
+      <c r="H42" s="17"/>
       <c r="I42" s="6"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -3548,28 +3563,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E44" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F44" s="15" t="s">
+      <c r="F44" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G44" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H44" s="16" t="s">
-        <v>83</v>
+      <c r="H44" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="1"/>
@@ -3592,23 +3607,23 @@
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="5"/>
       <c r="B45" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C45" s="2">
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E45" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="F45" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G45" s="6"/>
-      <c r="H45" s="16" t="s">
-        <v>85</v>
+      <c r="H45" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="I45" s="6"/>
       <c r="J45" s="1"/>
@@ -3631,23 +3646,23 @@
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="5"/>
       <c r="B46" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C46" s="2">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E46" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="15" t="s">
+      <c r="F46" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G46" s="6"/>
-      <c r="H46" s="16" t="s">
-        <v>87</v>
+      <c r="H46" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="1"/>
@@ -3670,21 +3685,21 @@
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="5"/>
       <c r="B47" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C47" s="2">
         <v>4</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E47" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G47" s="14" t="s">
+      <c r="F47" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="15" t="s">
         <v>15</v>
       </c>
       <c r="H47" s="7"/>
@@ -3709,21 +3724,21 @@
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="5"/>
       <c r="B48" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C48" s="2">
         <v>5</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E48" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F48" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G48" s="14" t="s">
+      <c r="F48" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" s="15" t="s">
         <v>15</v>
       </c>
       <c r="H48" s="7"/>
@@ -3748,25 +3763,25 @@
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="5"/>
       <c r="B49" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C49" s="2">
         <v>6</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E49" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E49" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F49" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G49" s="14" t="s">
+      <c r="F49" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="15" t="s">
         <v>15</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I49" s="6"/>
       <c r="J49" s="1"/>
@@ -3789,21 +3804,21 @@
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="5"/>
       <c r="B50" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C50" s="2">
         <v>7</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E50" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E50" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G50" s="14" t="s">
+      <c r="F50" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="15" t="s">
         <v>15</v>
       </c>
       <c r="H50" s="7"/>
@@ -3828,23 +3843,23 @@
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="5"/>
       <c r="B51" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C51" s="2">
         <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E51" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F51" s="17" t="s">
-        <v>27</v>
+      <c r="F51" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I51" s="6"/>
       <c r="J51" s="1"/>
@@ -3867,23 +3882,23 @@
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="5"/>
       <c r="B52" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C52" s="2">
         <v>9</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E52" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F52" s="19" t="s">
-        <v>63</v>
+      <c r="F52" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G52" s="6"/>
-      <c r="H52" s="16" t="s">
-        <v>95</v>
+      <c r="H52" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="1"/>
@@ -3906,19 +3921,19 @@
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="5"/>
       <c r="B53" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C53" s="2">
         <v>10</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E53" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E53" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="19" t="s">
-        <v>63</v>
+      <c r="F53" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="7"/>
@@ -3943,19 +3958,19 @@
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="5"/>
       <c r="B54" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C54" s="2">
         <v>11</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>63</v>
+        <v>99</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="7"/>
@@ -3978,7 +3993,7 @@
       <c r="Y54" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
-      <c r="A55" s="23"/>
+      <c r="A55" s="24"/>
       <c r="B55" s="6"/>
       <c r="C55" s="2"/>
       <c r="D55" s="5"/>
@@ -4032,29 +4047,29 @@
       <c r="Y56" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
-      <c r="A57" s="24" t="s">
-        <v>99</v>
+      <c r="A57" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E57" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G57" s="14" t="s">
+      <c r="F57" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G57" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H57" s="25" t="s">
-        <v>101</v>
+      <c r="H57" s="26" t="s">
+        <v>102</v>
       </c>
       <c r="I57" s="6"/>
       <c r="J57" s="1"/>
@@ -4077,23 +4092,23 @@
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="5"/>
       <c r="B58" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C58" s="2">
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E58" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F58" s="17" t="s">
-        <v>27</v>
+      <c r="F58" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G58" s="6"/>
-      <c r="H58" s="25" t="s">
-        <v>103</v>
+      <c r="H58" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="1"/>
@@ -4116,25 +4131,25 @@
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="5"/>
       <c r="B59" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C59" s="2">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E59" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E59" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F59" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G59" s="14" t="s">
+      <c r="F59" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H59" s="25" t="s">
-        <v>105</v>
+      <c r="H59" s="26" t="s">
+        <v>106</v>
       </c>
       <c r="I59" s="6"/>
       <c r="J59" s="1"/>
@@ -4157,23 +4172,23 @@
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="5"/>
       <c r="B60" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C60" s="2">
         <v>4</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E60" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="E60" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="17" t="s">
-        <v>27</v>
+      <c r="F60" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G60" s="6"/>
-      <c r="H60" s="25" t="s">
-        <v>107</v>
+      <c r="H60" s="26" t="s">
+        <v>108</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="1"/>
@@ -4196,23 +4211,23 @@
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
       <c r="A61" s="5"/>
       <c r="B61" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C61" s="2">
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E61" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E61" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F61" s="17" t="s">
-        <v>27</v>
+      <c r="F61" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G61" s="6"/>
-      <c r="H61" s="25" t="s">
-        <v>109</v>
+      <c r="H61" s="26" t="s">
+        <v>110</v>
       </c>
       <c r="I61" s="6"/>
       <c r="J61" s="1"/>
@@ -4235,24 +4250,24 @@
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
       <c r="A62" s="5"/>
       <c r="B62" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C62" s="2">
         <v>6</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E62" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E62" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F62" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G62" s="14" t="s">
+      <c r="F62" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H62" s="25" t="s">
+      <c r="H62" s="26" t="s">
         <v>18</v>
       </c>
       <c r="I62" s="6"/>
@@ -4276,25 +4291,25 @@
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
       <c r="A63" s="5"/>
       <c r="B63" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C63" s="2">
         <v>7</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E63" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F63" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G63" s="14" t="s">
+      <c r="F63" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H63" s="26" t="s">
-        <v>112</v>
+      <c r="H63" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="I63" s="6"/>
       <c r="J63" s="1"/>
@@ -4317,23 +4332,23 @@
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
       <c r="A64" s="5"/>
       <c r="B64" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C64" s="2">
         <v>8</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E64" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E64" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F64" s="17" t="s">
-        <v>27</v>
+      <c r="F64" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G64" s="6"/>
-      <c r="H64" s="25" t="s">
-        <v>113</v>
+      <c r="H64" s="26" t="s">
+        <v>114</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="1"/>
@@ -4356,25 +4371,25 @@
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
       <c r="A65" s="5"/>
       <c r="B65" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C65" s="2">
         <v>9</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E65" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E65" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F65" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G65" s="14" t="s">
+      <c r="F65" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G65" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H65" s="25" t="s">
-        <v>115</v>
+      <c r="H65" s="26" t="s">
+        <v>116</v>
       </c>
       <c r="I65" s="6"/>
       <c r="J65" s="1"/>
@@ -4397,25 +4412,25 @@
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
       <c r="A66" s="5"/>
       <c r="B66" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C66" s="2">
         <v>10</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E66" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="E66" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G66" s="14" t="s">
+      <c r="F66" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H66" s="26" t="s">
-        <v>117</v>
+      <c r="H66" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="1"/>
@@ -4438,23 +4453,23 @@
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
       <c r="A67" s="5"/>
       <c r="B67" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C67" s="2">
         <v>11</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E67" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E67" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F67" s="19" t="s">
-        <v>63</v>
+      <c r="F67" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G67" s="6"/>
-      <c r="H67" s="26" t="s">
-        <v>118</v>
+      <c r="H67" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="I67" s="6"/>
       <c r="J67" s="1"/>
@@ -4529,29 +4544,29 @@
       <c r="Y69" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
-      <c r="A70" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B70" s="6" t="s">
+      <c r="A70" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E70" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F70" s="15" t="s">
+      <c r="F70" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G70" s="14" t="s">
+      <c r="G70" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H70" s="25" t="s">
-        <v>121</v>
+      <c r="H70" s="26" t="s">
+        <v>122</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="1"/>
@@ -4573,26 +4588,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
       <c r="A71" s="5"/>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="2">
         <v>2</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E71" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="E71" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="15" t="s">
+      <c r="F71" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G71" s="14" t="s">
+      <c r="G71" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H71" s="25" t="s">
-        <v>123</v>
+      <c r="H71" s="26" t="s">
+        <v>124</v>
       </c>
       <c r="I71" s="6"/>
       <c r="J71" s="1"/>
@@ -4614,26 +4629,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="5"/>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="2">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E72" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E72" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="15" t="s">
+      <c r="F72" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G72" s="14" t="s">
+      <c r="G72" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H72" s="25" t="s">
-        <v>125</v>
+      <c r="H72" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="1"/>
@@ -4655,24 +4670,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
       <c r="A73" s="5"/>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="2">
         <v>4</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E73" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E73" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F73" s="15" t="s">
+      <c r="F73" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G73" s="6"/>
-      <c r="H73" s="25" t="s">
-        <v>127</v>
+      <c r="H73" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="I73" s="6"/>
       <c r="J73" s="1"/>
@@ -4694,26 +4709,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="5"/>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="2">
         <v>5</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E74" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E74" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F74" s="15" t="s">
+      <c r="F74" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G74" s="14" t="s">
+      <c r="G74" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H74" s="25" t="s">
-        <v>129</v>
+      <c r="H74" s="26" t="s">
+        <v>130</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="1"/>
@@ -4735,26 +4750,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="5"/>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="2">
         <v>6</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E75" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E75" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F75" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G75" s="14" t="s">
+      <c r="F75" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G75" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H75" s="25" t="s">
-        <v>131</v>
+      <c r="H75" s="26" t="s">
+        <v>132</v>
       </c>
       <c r="I75" s="6"/>
       <c r="J75" s="1"/>
@@ -4776,26 +4791,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="5"/>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="2">
         <v>7</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E76" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E76" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F76" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G76" s="14" t="s">
+      <c r="F76" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G76" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H76" s="26" t="s">
-        <v>133</v>
+      <c r="H76" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="1"/>
@@ -4817,26 +4832,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="5"/>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="2">
         <v>8</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E77" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E77" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F77" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G77" s="14" t="s">
+      <c r="F77" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G77" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H77" s="25" t="s">
-        <v>135</v>
+      <c r="H77" s="26" t="s">
+        <v>136</v>
       </c>
       <c r="I77" s="6"/>
       <c r="J77" s="1"/>
@@ -4858,24 +4873,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="5"/>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="2">
         <v>9</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E78" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="E78" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F78" s="17" t="s">
-        <v>27</v>
+      <c r="F78" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G78" s="6"/>
-      <c r="H78" s="26" t="s">
-        <v>137</v>
+      <c r="H78" s="27" t="s">
+        <v>138</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="1"/>
@@ -4897,24 +4912,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="5"/>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="2">
         <v>10</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E79" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E79" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F79" s="17" t="s">
-        <v>27</v>
+      <c r="F79" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G79" s="6"/>
-      <c r="H79" s="25" t="s">
-        <v>139</v>
+      <c r="H79" s="26" t="s">
+        <v>140</v>
       </c>
       <c r="I79" s="6"/>
       <c r="J79" s="1"/>
@@ -4936,26 +4951,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
       <c r="A80" s="5"/>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="2">
         <v>11</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E80" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E80" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F80" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G80" s="14" t="s">
+      <c r="F80" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H80" s="26" t="s">
-        <v>141</v>
+      <c r="H80" s="27" t="s">
+        <v>142</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="1"/>
@@ -4977,24 +4992,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
       <c r="A81" s="5"/>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="2">
         <v>12</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E81" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="E81" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F81" s="17" t="s">
-        <v>27</v>
+      <c r="F81" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G81" s="6"/>
-      <c r="H81" s="26" t="s">
-        <v>143</v>
+      <c r="H81" s="27" t="s">
+        <v>144</v>
       </c>
       <c r="I81" s="6"/>
       <c r="J81" s="1"/>
@@ -5016,26 +5031,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
       <c r="A82" s="5"/>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="2">
         <v>13</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E82" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E82" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F82" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G82" s="14" t="s">
+      <c r="F82" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G82" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H82" s="26" t="s">
-        <v>145</v>
+      <c r="H82" s="27" t="s">
+        <v>146</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="1"/>
@@ -5110,29 +5125,29 @@
       <c r="Y84" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
-      <c r="A85" s="27" t="s">
-        <v>146</v>
+      <c r="A85" s="28" t="s">
+        <v>147</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>11</v>
+        <v>148</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E85" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E85" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="15" t="s">
+      <c r="F85" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G85" s="14" t="s">
+      <c r="G85" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H85" s="25" t="s">
-        <v>148</v>
+      <c r="H85" s="26" t="s">
+        <v>150</v>
       </c>
       <c r="I85" s="6"/>
       <c r="J85" s="1"/>
@@ -5155,25 +5170,25 @@
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
       <c r="A86" s="5"/>
       <c r="B86" s="6" t="s">
-        <v>11</v>
+        <v>148</v>
       </c>
       <c r="C86" s="2">
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E86" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E86" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F86" s="15" t="s">
+      <c r="F86" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G86" s="14" t="s">
+      <c r="G86" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H86" s="26" t="s">
-        <v>150</v>
+      <c r="H86" s="27" t="s">
+        <v>152</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="1"/>
@@ -5195,26 +5210,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
       <c r="A87" s="5"/>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="2">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E87" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E87" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="15" t="s">
+      <c r="F87" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G87" s="14" t="s">
+      <c r="G87" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H87" s="25" t="s">
-        <v>152</v>
+      <c r="H87" s="26" t="s">
+        <v>154</v>
       </c>
       <c r="I87" s="6"/>
       <c r="J87" s="1"/>
@@ -5236,26 +5251,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
       <c r="A88" s="5"/>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C88" s="2">
         <v>4</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E88" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="E88" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="15" t="s">
+      <c r="F88" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G88" s="14" t="s">
+      <c r="G88" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H88" s="25" t="s">
-        <v>154</v>
+      <c r="H88" s="26" t="s">
+        <v>156</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="1"/>
@@ -5277,26 +5292,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
       <c r="A89" s="5"/>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C89" s="2">
         <v>5</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E89" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="E89" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F89" s="15" t="s">
+      <c r="F89" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G89" s="14" t="s">
+      <c r="G89" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H89" s="25" t="s">
-        <v>156</v>
+      <c r="H89" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="I89" s="6"/>
       <c r="J89" s="1"/>
@@ -5318,24 +5333,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
       <c r="A90" s="5"/>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C90" s="2">
         <v>6</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E90" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E90" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F90" s="15" t="s">
+      <c r="F90" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G90" s="6"/>
-      <c r="H90" s="25" t="s">
-        <v>158</v>
+      <c r="H90" s="26" t="s">
+        <v>160</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="1"/>
@@ -5355,26 +5370,26 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
       <c r="A91" s="5"/>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C91" s="2">
         <v>7</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E91" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E91" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F91" s="15" t="s">
+      <c r="F91" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G91" s="6"/>
-      <c r="H91" s="26" t="s">
-        <v>160</v>
+      <c r="H91" s="27" t="s">
+        <v>162</v>
       </c>
       <c r="I91" s="6"/>
       <c r="J91" s="1"/>
@@ -5394,28 +5409,28 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
       <c r="A92" s="5"/>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C92" s="2">
         <v>8</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E92" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E92" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F92" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G92" s="14" t="s">
+      <c r="F92" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G92" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H92" s="25" t="s">
-        <v>162</v>
+      <c r="H92" s="26" t="s">
+        <v>164</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="1"/>
@@ -5435,28 +5450,28 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
       <c r="A93" s="5"/>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C93" s="2">
         <v>9</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E93" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="E93" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F93" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G93" s="14" t="s">
+      <c r="F93" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G93" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H93" s="25" t="s">
-        <v>164</v>
+      <c r="H93" s="26" t="s">
+        <v>166</v>
       </c>
       <c r="I93" s="6"/>
       <c r="J93" s="1"/>
@@ -5476,28 +5491,28 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
       <c r="A94" s="5"/>
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C94" s="2">
         <v>10</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E94" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="E94" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F94" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G94" s="14" t="s">
+      <c r="F94" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G94" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H94" s="25" t="s">
-        <v>166</v>
+      <c r="H94" s="26" t="s">
+        <v>168</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="1"/>
@@ -5517,28 +5532,28 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="5"/>
-      <c r="B95" s="6" t="s">
+      <c r="B95" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C95" s="2">
         <v>11</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E95" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="E95" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G95" s="14" t="s">
+      <c r="F95" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H95" s="26" t="s">
-        <v>168</v>
+      <c r="H95" s="27" t="s">
+        <v>170</v>
       </c>
       <c r="I95" s="6"/>
       <c r="J95" s="1"/>
@@ -5558,28 +5573,28 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="19.5">
       <c r="A96" s="5"/>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C96" s="2">
         <v>12</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E96" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="E96" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F96" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G96" s="14" t="s">
+      <c r="F96" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H96" s="25" t="s">
-        <v>170</v>
+      <c r="H96" s="26" t="s">
+        <v>172</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="1"/>
@@ -5599,26 +5614,26 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="19.5">
       <c r="A97" s="5"/>
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C97" s="2">
         <v>13</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E97" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E97" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F97" s="17" t="s">
-        <v>27</v>
+      <c r="F97" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G97" s="6"/>
-      <c r="H97" s="25" t="s">
-        <v>172</v>
+      <c r="H97" s="26" t="s">
+        <v>174</v>
       </c>
       <c r="I97" s="6"/>
       <c r="J97" s="1"/>
@@ -5638,28 +5653,28 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="19.5">
       <c r="A98" s="5"/>
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C98" s="2">
         <v>14</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E98" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E98" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F98" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G98" s="14" t="s">
+      <c r="F98" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H98" s="25" t="s">
-        <v>174</v>
+      <c r="H98" s="26" t="s">
+        <v>176</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="1"/>
@@ -5679,28 +5694,28 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="19.5">
       <c r="A99" s="5"/>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C99" s="2">
         <v>15</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E99" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="E99" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F99" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G99" s="14" t="s">
+      <c r="F99" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G99" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H99" s="26" t="s">
-        <v>176</v>
+      <c r="H99" s="27" t="s">
+        <v>178</v>
       </c>
       <c r="I99" s="6"/>
       <c r="J99" s="1"/>
@@ -5720,7 +5735,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="19.5">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="2"/>
@@ -5747,7 +5762,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="19.5">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="2"/>
@@ -5774,30 +5789,30 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
-      <c r="A102" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="B102" s="6" t="s">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="19.5">
+      <c r="A102" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B102" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E102" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="E102" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F102" s="15" t="s">
+      <c r="F102" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G102" s="22" t="s">
+      <c r="G102" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H102" s="26" t="s">
-        <v>179</v>
+      <c r="H102" s="27" t="s">
+        <v>181</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="1"/>
@@ -5817,28 +5832,28 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="19.5">
       <c r="A103" s="5"/>
-      <c r="B103" s="6" t="s">
+      <c r="B103" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C103" s="2">
         <v>2</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E103" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E103" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F103" s="15" t="s">
+      <c r="F103" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G103" s="14" t="s">
+      <c r="G103" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H103" s="26" t="s">
-        <v>181</v>
+      <c r="H103" s="27" t="s">
+        <v>183</v>
       </c>
       <c r="I103" s="6"/>
       <c r="J103" s="1"/>
@@ -5858,28 +5873,28 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="19.5">
       <c r="A104" s="5"/>
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C104" s="2">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E104" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E104" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F104" s="15" t="s">
+      <c r="F104" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G104" s="14" t="s">
+      <c r="G104" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H104" s="26" t="s">
-        <v>183</v>
+      <c r="H104" s="27" t="s">
+        <v>185</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="1"/>
@@ -5901,24 +5916,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25">
       <c r="A105" s="5"/>
-      <c r="B105" s="6" t="s">
+      <c r="B105" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C105" s="2">
         <v>4</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E105" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="E105" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F105" s="15" t="s">
+      <c r="F105" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G105" s="6"/>
-      <c r="H105" s="25" t="s">
-        <v>185</v>
+      <c r="H105" s="26" t="s">
+        <v>187</v>
       </c>
       <c r="I105" s="6"/>
       <c r="J105" s="1"/>
@@ -5940,26 +5955,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25">
       <c r="A106" s="5"/>
-      <c r="B106" s="6" t="s">
+      <c r="B106" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C106" s="2">
         <v>5</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E106" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="E106" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F106" s="15" t="s">
+      <c r="F106" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G106" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="H106" s="26" t="s">
-        <v>188</v>
+      <c r="G106" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="H106" s="27" t="s">
+        <v>190</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="1"/>
@@ -5981,26 +5996,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25">
       <c r="A107" s="5"/>
-      <c r="B107" s="6" t="s">
+      <c r="B107" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C107" s="2">
         <v>6</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E107" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E107" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F107" s="15" t="s">
+      <c r="F107" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G107" s="14" t="s">
+      <c r="G107" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H107" s="25" t="s">
-        <v>190</v>
+      <c r="H107" s="26" t="s">
+        <v>192</v>
       </c>
       <c r="I107" s="6"/>
       <c r="J107" s="1"/>
@@ -6022,26 +6037,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25">
       <c r="A108" s="5"/>
-      <c r="B108" s="6" t="s">
+      <c r="B108" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C108" s="2">
         <v>7</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E108" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E108" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="15" t="s">
+      <c r="F108" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G108" s="14" t="s">
+      <c r="G108" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H108" s="26" t="s">
-        <v>192</v>
+      <c r="H108" s="27" t="s">
+        <v>194</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="1"/>
@@ -6063,26 +6078,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25">
       <c r="A109" s="5"/>
-      <c r="B109" s="6" t="s">
+      <c r="B109" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C109" s="2">
         <v>8</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E109" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="E109" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F109" s="15" t="s">
+      <c r="F109" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G109" s="14" t="s">
+      <c r="G109" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H109" s="26" t="s">
-        <v>194</v>
+      <c r="H109" s="27" t="s">
+        <v>196</v>
       </c>
       <c r="I109" s="6"/>
       <c r="J109" s="1"/>
@@ -6104,24 +6119,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25">
       <c r="A110" s="5"/>
-      <c r="B110" s="6" t="s">
+      <c r="B110" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C110" s="2">
         <v>9</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E110" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E110" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F110" s="15" t="s">
+      <c r="F110" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G110" s="6"/>
-      <c r="H110" s="25" t="s">
-        <v>196</v>
+      <c r="H110" s="26" t="s">
+        <v>198</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="1"/>
@@ -6143,26 +6158,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25">
       <c r="A111" s="5"/>
-      <c r="B111" s="6" t="s">
+      <c r="B111" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C111" s="2">
         <v>10</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E111" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E111" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F111" s="15" t="s">
+      <c r="F111" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G111" s="14" t="s">
+      <c r="G111" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H111" s="25" t="s">
-        <v>198</v>
+      <c r="H111" s="26" t="s">
+        <v>200</v>
       </c>
       <c r="I111" s="6"/>
       <c r="J111" s="1"/>
@@ -6184,24 +6199,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25">
       <c r="A112" s="5"/>
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C112" s="2">
         <v>11</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E112" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E112" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F112" s="15" t="s">
+      <c r="F112" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G112" s="6"/>
-      <c r="H112" s="25" t="s">
-        <v>200</v>
+      <c r="H112" s="26" t="s">
+        <v>202</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="1"/>
@@ -6223,26 +6238,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25">
       <c r="A113" s="5"/>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C113" s="2">
         <v>12</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E113" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="E113" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F113" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G113" s="14" t="s">
+      <c r="F113" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G113" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H113" s="25" t="s">
-        <v>202</v>
+      <c r="H113" s="26" t="s">
+        <v>204</v>
       </c>
       <c r="I113" s="6"/>
       <c r="J113" s="1"/>
@@ -6264,24 +6279,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25">
       <c r="A114" s="5"/>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C114" s="2">
         <v>13</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E114" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E114" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F114" s="17" t="s">
-        <v>27</v>
+      <c r="F114" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G114" s="6"/>
-      <c r="H114" s="25" t="s">
-        <v>204</v>
+      <c r="H114" s="26" t="s">
+        <v>206</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="1"/>
@@ -6303,24 +6318,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25">
       <c r="A115" s="5"/>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C115" s="2">
         <v>14</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E115" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="E115" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F115" s="17" t="s">
-        <v>27</v>
+      <c r="F115" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G115" s="6"/>
-      <c r="H115" s="25" t="s">
-        <v>206</v>
+      <c r="H115" s="26" t="s">
+        <v>208</v>
       </c>
       <c r="I115" s="6"/>
       <c r="J115" s="1"/>
@@ -6342,26 +6357,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
       <c r="A116" s="5"/>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C116" s="2">
         <v>15</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E116" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="E116" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F116" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G116" s="14" t="s">
+      <c r="F116" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H116" s="25" t="s">
-        <v>208</v>
+      <c r="H116" s="26" t="s">
+        <v>210</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="1"/>
@@ -6383,26 +6398,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
       <c r="A117" s="5"/>
-      <c r="B117" s="6" t="s">
+      <c r="B117" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C117" s="2">
         <v>16</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E117" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F117" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G117" s="14" t="s">
+      <c r="F117" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G117" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H117" s="25" t="s">
-        <v>210</v>
+      <c r="H117" s="26" t="s">
+        <v>212</v>
       </c>
       <c r="I117" s="6"/>
       <c r="J117" s="1"/>
@@ -6424,26 +6439,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25">
       <c r="A118" s="5"/>
-      <c r="B118" s="6" t="s">
+      <c r="B118" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C118" s="2">
         <v>17</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E118" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="E118" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F118" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G118" s="14" t="s">
+      <c r="F118" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H118" s="25" t="s">
-        <v>212</v>
+      <c r="H118" s="26" t="s">
+        <v>214</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="1"/>
@@ -6465,26 +6480,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
       <c r="A119" s="5"/>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C119" s="2">
         <v>18</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E119" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="E119" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F119" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G119" s="14" t="s">
+      <c r="F119" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H119" s="25" t="s">
-        <v>214</v>
+      <c r="H119" s="26" t="s">
+        <v>216</v>
       </c>
       <c r="I119" s="6"/>
       <c r="J119" s="1"/>
@@ -6506,24 +6521,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25">
       <c r="A120" s="5"/>
-      <c r="B120" s="6" t="s">
+      <c r="B120" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C120" s="2">
         <v>19</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E120" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E120" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F120" s="17" t="s">
-        <v>27</v>
+      <c r="F120" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G120" s="6"/>
-      <c r="H120" s="26" t="s">
-        <v>216</v>
+      <c r="H120" s="27" t="s">
+        <v>218</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="1"/>
@@ -6545,26 +6560,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25">
       <c r="A121" s="5"/>
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C121" s="2">
         <v>20</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E121" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E121" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F121" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G121" s="14" t="s">
+      <c r="F121" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G121" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H121" s="26" t="s">
-        <v>218</v>
+      <c r="H121" s="27" t="s">
+        <v>220</v>
       </c>
       <c r="I121" s="6"/>
       <c r="J121" s="1"/>
@@ -6586,26 +6601,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25">
       <c r="A122" s="5"/>
-      <c r="B122" s="6" t="s">
+      <c r="B122" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C122" s="2">
         <v>21</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E122" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E122" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F122" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G122" s="14" t="s">
+      <c r="F122" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H122" s="26" t="s">
-        <v>220</v>
+      <c r="H122" s="27" t="s">
+        <v>222</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="1"/>
@@ -6627,24 +6642,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25">
       <c r="A123" s="5"/>
-      <c r="B123" s="6" t="s">
+      <c r="B123" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C123" s="2">
         <v>22</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E123" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E123" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F123" s="17" t="s">
-        <v>27</v>
+      <c r="F123" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G123" s="6"/>
-      <c r="H123" s="25" t="s">
-        <v>222</v>
+      <c r="H123" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="I123" s="6"/>
       <c r="J123" s="1"/>
@@ -6666,24 +6681,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25">
       <c r="A124" s="5"/>
-      <c r="B124" s="6" t="s">
+      <c r="B124" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C124" s="2">
         <v>23</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E124" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="E124" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F124" s="19" t="s">
-        <v>63</v>
+      <c r="F124" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G124" s="6"/>
-      <c r="H124" s="25" t="s">
-        <v>224</v>
+      <c r="H124" s="26" t="s">
+        <v>226</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="1"/>
@@ -6705,24 +6720,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25">
       <c r="A125" s="5"/>
-      <c r="B125" s="6" t="s">
+      <c r="B125" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C125" s="2">
         <v>24</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E125" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E125" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F125" s="19" t="s">
-        <v>63</v>
+      <c r="F125" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G125" s="6"/>
-      <c r="H125" s="25" t="s">
-        <v>226</v>
+      <c r="H125" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="I125" s="6"/>
       <c r="J125" s="1"/>
@@ -6797,27 +6812,27 @@
       <c r="Y127" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25">
-      <c r="A128" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="B128" s="6" t="s">
+      <c r="A128" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="B128" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E128" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="E128" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F128" s="15" t="s">
+      <c r="F128" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G128" s="6"/>
-      <c r="H128" s="25" t="s">
-        <v>229</v>
+      <c r="H128" s="26" t="s">
+        <v>231</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="1"/>
@@ -6839,26 +6854,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25">
       <c r="A129" s="5"/>
-      <c r="B129" s="6" t="s">
+      <c r="B129" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C129" s="2">
         <v>2</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E129" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="E129" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F129" s="15" t="s">
+      <c r="F129" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G129" s="14" t="s">
+      <c r="G129" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H129" s="26" t="s">
-        <v>231</v>
+      <c r="H129" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="I129" s="6"/>
       <c r="J129" s="1"/>
@@ -6880,26 +6895,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25">
       <c r="A130" s="5"/>
-      <c r="B130" s="6" t="s">
+      <c r="B130" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C130" s="2">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E130" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="E130" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F130" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G130" s="14" t="s">
+      <c r="F130" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G130" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H130" s="25" t="s">
-        <v>233</v>
+      <c r="H130" s="26" t="s">
+        <v>235</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="1"/>
@@ -6921,26 +6936,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25">
       <c r="A131" s="5"/>
-      <c r="B131" s="6" t="s">
+      <c r="B131" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C131" s="2">
         <v>4</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E131" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="E131" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F131" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G131" s="14" t="s">
+      <c r="F131" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G131" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H131" s="25" t="s">
-        <v>235</v>
+      <c r="H131" s="26" t="s">
+        <v>237</v>
       </c>
       <c r="I131" s="6"/>
       <c r="J131" s="1"/>
@@ -6962,26 +6977,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25">
       <c r="A132" s="5"/>
-      <c r="B132" s="6" t="s">
+      <c r="B132" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C132" s="2">
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E132" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="E132" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F132" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G132" s="14" t="s">
+      <c r="F132" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G132" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H132" s="25" t="s">
-        <v>237</v>
+      <c r="H132" s="26" t="s">
+        <v>239</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="1"/>
@@ -7003,26 +7018,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25">
       <c r="A133" s="5"/>
-      <c r="B133" s="6" t="s">
+      <c r="B133" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C133" s="2">
         <v>6</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E133" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E133" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F133" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G133" s="14" t="s">
+      <c r="F133" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G133" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H133" s="26" t="s">
-        <v>239</v>
+      <c r="H133" s="27" t="s">
+        <v>241</v>
       </c>
       <c r="I133" s="6"/>
       <c r="J133" s="1"/>
@@ -7044,26 +7059,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25">
       <c r="A134" s="5"/>
-      <c r="B134" s="6" t="s">
+      <c r="B134" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C134" s="2">
         <v>7</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E134" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="E134" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F134" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G134" s="14" t="s">
+      <c r="F134" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G134" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H134" s="26" t="s">
-        <v>241</v>
+      <c r="H134" s="27" t="s">
+        <v>243</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="1"/>
@@ -7085,26 +7100,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25">
       <c r="A135" s="5"/>
-      <c r="B135" s="6" t="s">
+      <c r="B135" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C135" s="2">
         <v>8</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="E135" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="E135" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F135" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G135" s="14" t="s">
+      <c r="F135" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G135" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H135" s="25" t="s">
-        <v>243</v>
+      <c r="H135" s="26" t="s">
+        <v>245</v>
       </c>
       <c r="I135" s="6"/>
       <c r="J135" s="1"/>
@@ -7126,26 +7141,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25">
       <c r="A136" s="5"/>
-      <c r="B136" s="6" t="s">
+      <c r="B136" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C136" s="2">
         <v>9</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E136" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="E136" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F136" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G136" s="14" t="s">
+      <c r="F136" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G136" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H136" s="26" t="s">
-        <v>245</v>
+      <c r="H136" s="27" t="s">
+        <v>247</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="1"/>
@@ -7167,24 +7182,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25">
       <c r="A137" s="5"/>
-      <c r="B137" s="6" t="s">
+      <c r="B137" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C137" s="2">
         <v>10</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E137" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="E137" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F137" s="17" t="s">
-        <v>27</v>
+      <c r="F137" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G137" s="6"/>
-      <c r="H137" s="25" t="s">
-        <v>247</v>
+      <c r="H137" s="26" t="s">
+        <v>249</v>
       </c>
       <c r="I137" s="6"/>
       <c r="J137" s="1"/>
@@ -7206,26 +7221,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25">
       <c r="A138" s="5"/>
-      <c r="B138" s="6" t="s">
+      <c r="B138" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C138" s="2">
         <v>11</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E138" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="E138" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F138" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G138" s="14" t="s">
+      <c r="F138" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G138" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H138" s="25" t="s">
-        <v>249</v>
+      <c r="H138" s="26" t="s">
+        <v>251</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="1"/>
@@ -7247,26 +7262,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25">
       <c r="A139" s="5"/>
-      <c r="B139" s="6" t="s">
+      <c r="B139" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C139" s="2">
         <v>12</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E139" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="E139" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F139" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G139" s="14" t="s">
+      <c r="F139" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G139" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H139" s="25" t="s">
-        <v>251</v>
+      <c r="H139" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="I139" s="6"/>
       <c r="J139" s="1"/>
@@ -7288,26 +7303,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25">
       <c r="A140" s="5"/>
-      <c r="B140" s="6" t="s">
+      <c r="B140" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C140" s="2">
         <v>13</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E140" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="E140" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F140" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G140" s="14" t="s">
+      <c r="F140" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G140" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H140" s="26" t="s">
-        <v>253</v>
+      <c r="H140" s="27" t="s">
+        <v>255</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="1"/>
@@ -7329,24 +7344,24 @@
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25">
       <c r="A141" s="5"/>
-      <c r="B141" s="6" t="s">
+      <c r="B141" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C141" s="2">
         <v>14</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E141" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="E141" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F141" s="19" t="s">
-        <v>63</v>
+      <c r="F141" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G141" s="6"/>
-      <c r="H141" s="26" t="s">
-        <v>255</v>
+      <c r="H141" s="27" t="s">
+        <v>257</v>
       </c>
       <c r="I141" s="6"/>
       <c r="J141" s="1"/>
@@ -7368,26 +7383,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25">
       <c r="A142" s="5"/>
-      <c r="B142" s="6" t="s">
+      <c r="B142" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C142" s="2">
         <v>15</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E142" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="E142" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F142" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G142" s="14" t="s">
+      <c r="F142" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G142" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H142" s="25" t="s">
-        <v>257</v>
+      <c r="H142" s="26" t="s">
+        <v>259</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="1"/>
@@ -7462,27 +7477,27 @@
       <c r="Y144" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
-      <c r="A145" s="27" t="s">
-        <v>258</v>
+      <c r="A145" s="28" t="s">
+        <v>260</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C145" s="2">
         <v>1</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E145" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="F145" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E145" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="F145" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G145" s="6"/>
-      <c r="H145" s="25" t="s">
-        <v>261</v>
+      <c r="H145" s="26" t="s">
+        <v>263</v>
       </c>
       <c r="I145" s="6"/>
       <c r="J145" s="1"/>
@@ -7505,23 +7520,23 @@
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25">
       <c r="A146" s="5"/>
       <c r="B146" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C146" s="2">
         <v>2</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E146" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="F146" s="17" t="s">
-        <v>27</v>
+        <v>264</v>
+      </c>
+      <c r="E146" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="F146" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G146" s="6"/>
-      <c r="H146" s="25" t="s">
-        <v>264</v>
+      <c r="H146" s="26" t="s">
+        <v>266</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="1"/>
@@ -7544,23 +7559,23 @@
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25">
       <c r="A147" s="5"/>
       <c r="B147" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C147" s="2">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E147" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="F147" s="17" t="s">
-        <v>27</v>
+        <v>267</v>
+      </c>
+      <c r="E147" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="F147" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G147" s="6"/>
-      <c r="H147" s="25" t="s">
-        <v>267</v>
+      <c r="H147" s="26" t="s">
+        <v>269</v>
       </c>
       <c r="I147" s="6"/>
       <c r="J147" s="1"/>
@@ -7583,23 +7598,23 @@
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25">
       <c r="A148" s="5"/>
       <c r="B148" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C148" s="2">
         <v>4</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E148" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="F148" s="17" t="s">
-        <v>27</v>
+        <v>270</v>
+      </c>
+      <c r="E148" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="F148" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G148" s="6"/>
-      <c r="H148" s="25" t="s">
-        <v>270</v>
+      <c r="H148" s="26" t="s">
+        <v>272</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="1"/>
@@ -7622,23 +7637,23 @@
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25">
       <c r="A149" s="5"/>
       <c r="B149" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C149" s="2">
         <v>5</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E149" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="F149" s="19" t="s">
-        <v>63</v>
+        <v>273</v>
+      </c>
+      <c r="E149" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="F149" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G149" s="6"/>
-      <c r="H149" s="25" t="s">
-        <v>273</v>
+      <c r="H149" s="26" t="s">
+        <v>275</v>
       </c>
       <c r="I149" s="6"/>
       <c r="J149" s="1"/>
@@ -7661,23 +7676,23 @@
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25">
       <c r="A150" s="5"/>
       <c r="B150" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C150" s="2">
         <v>6</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E150" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="F150" s="19" t="s">
-        <v>63</v>
+        <v>276</v>
+      </c>
+      <c r="E150" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="F150" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G150" s="6"/>
-      <c r="H150" s="26" t="s">
-        <v>276</v>
+      <c r="H150" s="27" t="s">
+        <v>278</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="1"/>
@@ -7752,27 +7767,27 @@
       <c r="Y152" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25">
-      <c r="A153" s="27" t="s">
-        <v>277</v>
+      <c r="A153" s="28" t="s">
+        <v>279</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C153" s="2">
         <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E153" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="F153" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E153" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="F153" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G153" s="6"/>
-      <c r="H153" s="25" t="s">
-        <v>279</v>
+      <c r="H153" s="26" t="s">
+        <v>281</v>
       </c>
       <c r="I153" s="6"/>
       <c r="J153" s="1"/>
@@ -7795,23 +7810,23 @@
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25">
       <c r="A154" s="5"/>
       <c r="B154" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C154" s="2">
         <v>2</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="E154" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="F154" s="17" t="s">
-        <v>27</v>
+        <v>282</v>
+      </c>
+      <c r="E154" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="F154" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G154" s="6"/>
-      <c r="H154" s="25" t="s">
-        <v>282</v>
+      <c r="H154" s="26" t="s">
+        <v>284</v>
       </c>
       <c r="I154" s="6"/>
       <c r="J154" s="1"/>
@@ -7834,23 +7849,23 @@
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25">
       <c r="A155" s="5"/>
       <c r="B155" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C155" s="2">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E155" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="F155" s="17" t="s">
-        <v>27</v>
+        <v>285</v>
+      </c>
+      <c r="E155" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="F155" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G155" s="6"/>
-      <c r="H155" s="26" t="s">
-        <v>285</v>
+      <c r="H155" s="27" t="s">
+        <v>287</v>
       </c>
       <c r="I155" s="6"/>
       <c r="J155" s="1"/>
@@ -7873,23 +7888,23 @@
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25">
       <c r="A156" s="5"/>
       <c r="B156" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C156" s="2">
         <v>4</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E156" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="F156" s="17" t="s">
-        <v>27</v>
+        <v>288</v>
+      </c>
+      <c r="E156" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="F156" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G156" s="6"/>
-      <c r="H156" s="25" t="s">
-        <v>288</v>
+      <c r="H156" s="26" t="s">
+        <v>290</v>
       </c>
       <c r="I156" s="6"/>
       <c r="J156" s="1"/>
@@ -7912,23 +7927,23 @@
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25">
       <c r="A157" s="5"/>
       <c r="B157" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C157" s="2">
         <v>5</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E157" s="28" t="s">
-        <v>290</v>
-      </c>
-      <c r="F157" s="17" t="s">
-        <v>27</v>
+        <v>291</v>
+      </c>
+      <c r="E157" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="F157" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G157" s="6"/>
-      <c r="H157" s="26" t="s">
-        <v>285</v>
+      <c r="H157" s="27" t="s">
+        <v>287</v>
       </c>
       <c r="I157" s="6"/>
       <c r="J157" s="1"/>
@@ -7949,7 +7964,7 @@
       <c r="Y157" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25">
-      <c r="A158" s="29"/>
+      <c r="A158" s="30"/>
       <c r="B158" s="1"/>
       <c r="C158" s="2"/>
       <c r="D158" s="1"/>
@@ -8003,27 +8018,27 @@
       <c r="Y159" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
-      <c r="A160" s="27" t="s">
-        <v>291</v>
+      <c r="A160" s="28" t="s">
+        <v>293</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C160" s="2">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E160" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="F160" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="E160" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="F160" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G160" s="6"/>
-      <c r="H160" s="25" t="s">
-        <v>294</v>
+      <c r="H160" s="26" t="s">
+        <v>296</v>
       </c>
       <c r="I160" s="6"/>
       <c r="J160" s="1"/>
@@ -8046,25 +8061,25 @@
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25">
       <c r="A161" s="5"/>
       <c r="B161" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C161" s="2">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="E161" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="F161" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G161" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E161" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="F161" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G161" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H161" s="25" t="s">
-        <v>297</v>
+      <c r="H161" s="26" t="s">
+        <v>299</v>
       </c>
       <c r="I161" s="6"/>
       <c r="J161" s="1"/>
@@ -8087,25 +8102,25 @@
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25">
       <c r="A162" s="5"/>
       <c r="B162" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C162" s="2">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E162" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="E162" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="F162" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G162" s="14" t="s">
+      <c r="F162" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G162" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H162" s="25" t="s">
-        <v>299</v>
+      <c r="H162" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="I162" s="6"/>
       <c r="J162" s="1"/>
@@ -8128,23 +8143,23 @@
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25">
       <c r="A163" s="5"/>
       <c r="B163" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C163" s="2">
         <v>4</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E163" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="E163" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="F163" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G163" s="6"/>
+      <c r="H163" s="26" t="s">
         <v>301</v>
-      </c>
-      <c r="F163" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G163" s="6"/>
-      <c r="H163" s="25" t="s">
-        <v>299</v>
       </c>
       <c r="I163" s="6"/>
       <c r="J163" s="1"/>
@@ -8167,23 +8182,23 @@
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25">
       <c r="A164" s="5"/>
       <c r="B164" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C164" s="2">
         <v>5</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E164" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="F164" s="17" t="s">
-        <v>27</v>
+        <v>304</v>
+      </c>
+      <c r="E164" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="F164" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G164" s="6"/>
-      <c r="H164" s="25" t="s">
-        <v>303</v>
+      <c r="H164" s="26" t="s">
+        <v>305</v>
       </c>
       <c r="I164" s="6"/>
       <c r="J164" s="1"/>
@@ -8206,23 +8221,23 @@
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25">
       <c r="A165" s="5"/>
       <c r="B165" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C165" s="2">
         <v>6</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E165" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="F165" s="17" t="s">
-        <v>27</v>
+        <v>306</v>
+      </c>
+      <c r="E165" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="F165" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G165" s="6"/>
-      <c r="H165" s="25" t="s">
-        <v>306</v>
+      <c r="H165" s="26" t="s">
+        <v>308</v>
       </c>
       <c r="I165" s="6"/>
       <c r="J165" s="1"/>
@@ -8245,23 +8260,23 @@
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25">
       <c r="A166" s="5"/>
       <c r="B166" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C166" s="2">
         <v>7</v>
       </c>
       <c r="D166" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E166" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="E166" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="F166" s="17" t="s">
-        <v>27</v>
+      <c r="F166" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G166" s="6"/>
-      <c r="H166" s="25" t="s">
-        <v>308</v>
+      <c r="H166" s="26" t="s">
+        <v>310</v>
       </c>
       <c r="I166" s="6"/>
       <c r="J166" s="1"/>
@@ -8284,23 +8299,23 @@
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25">
       <c r="A167" s="5"/>
       <c r="B167" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C167" s="2">
         <v>8</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E167" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="F167" s="17" t="s">
-        <v>27</v>
+        <v>311</v>
+      </c>
+      <c r="E167" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="F167" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G167" s="6"/>
-      <c r="H167" s="25" t="s">
-        <v>311</v>
+      <c r="H167" s="26" t="s">
+        <v>313</v>
       </c>
       <c r="I167" s="6"/>
       <c r="J167" s="1"/>
@@ -8323,23 +8338,23 @@
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25">
       <c r="A168" s="5"/>
       <c r="B168" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C168" s="2">
         <v>9</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E168" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="F168" s="17" t="s">
-        <v>27</v>
+        <v>314</v>
+      </c>
+      <c r="E168" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="F168" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G168" s="6"/>
-      <c r="H168" s="25" t="s">
-        <v>314</v>
+      <c r="H168" s="26" t="s">
+        <v>316</v>
       </c>
       <c r="I168" s="6"/>
       <c r="J168" s="1"/>
@@ -8362,23 +8377,23 @@
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25">
       <c r="A169" s="5"/>
       <c r="B169" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C169" s="2">
         <v>10</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E169" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="F169" s="17" t="s">
-        <v>27</v>
+        <v>317</v>
+      </c>
+      <c r="E169" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="F169" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G169" s="6"/>
-      <c r="H169" s="26" t="s">
-        <v>317</v>
+      <c r="H169" s="27" t="s">
+        <v>319</v>
       </c>
       <c r="I169" s="6"/>
       <c r="J169" s="1"/>
@@ -8401,23 +8416,23 @@
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="17.25">
       <c r="A170" s="5"/>
       <c r="B170" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C170" s="2">
         <v>11</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E170" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="F170" s="17" t="s">
-        <v>27</v>
+        <v>320</v>
+      </c>
+      <c r="E170" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="F170" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G170" s="6"/>
-      <c r="H170" s="25" t="s">
-        <v>320</v>
+      <c r="H170" s="26" t="s">
+        <v>322</v>
       </c>
       <c r="I170" s="6"/>
       <c r="J170" s="1"/>
@@ -8440,23 +8455,23 @@
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="17.25">
       <c r="A171" s="5"/>
       <c r="B171" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C171" s="2">
         <v>12</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E171" s="28" t="s">
-        <v>322</v>
-      </c>
-      <c r="F171" s="17" t="s">
-        <v>27</v>
+        <v>323</v>
+      </c>
+      <c r="E171" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="F171" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G171" s="6"/>
-      <c r="H171" s="25" t="s">
-        <v>323</v>
+      <c r="H171" s="26" t="s">
+        <v>325</v>
       </c>
       <c r="I171" s="6"/>
       <c r="J171" s="1"/>
@@ -8479,23 +8494,23 @@
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="17.25">
       <c r="A172" s="5"/>
       <c r="B172" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C172" s="2">
         <v>13</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E172" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="F172" s="17" t="s">
-        <v>27</v>
+        <v>326</v>
+      </c>
+      <c r="E172" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="F172" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G172" s="6"/>
-      <c r="H172" s="25" t="s">
-        <v>326</v>
+      <c r="H172" s="26" t="s">
+        <v>328</v>
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="1"/>
@@ -8518,23 +8533,23 @@
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="17.25">
       <c r="A173" s="5"/>
       <c r="B173" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C173" s="2">
         <v>14</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="E173" s="28" t="s">
-        <v>328</v>
-      </c>
-      <c r="F173" s="17" t="s">
-        <v>27</v>
+        <v>329</v>
+      </c>
+      <c r="E173" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="F173" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G173" s="6"/>
-      <c r="H173" s="25" t="s">
-        <v>329</v>
+      <c r="H173" s="26" t="s">
+        <v>331</v>
       </c>
       <c r="I173" s="6"/>
       <c r="J173" s="1"/>
@@ -8557,23 +8572,23 @@
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="17.25">
       <c r="A174" s="5"/>
       <c r="B174" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C174" s="2">
         <v>15</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E174" s="28" t="s">
-        <v>330</v>
-      </c>
-      <c r="F174" s="17" t="s">
-        <v>27</v>
+        <v>173</v>
+      </c>
+      <c r="E174" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="F174" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G174" s="6"/>
-      <c r="H174" s="25" t="s">
-        <v>331</v>
+      <c r="H174" s="26" t="s">
+        <v>333</v>
       </c>
       <c r="I174" s="6"/>
       <c r="J174" s="1"/>
@@ -8596,23 +8611,23 @@
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="17.25">
       <c r="A175" s="5"/>
       <c r="B175" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C175" s="2">
         <v>16</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E175" s="28" t="s">
-        <v>333</v>
-      </c>
-      <c r="F175" s="17" t="s">
-        <v>27</v>
+        <v>334</v>
+      </c>
+      <c r="E175" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="F175" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G175" s="6"/>
-      <c r="H175" s="25" t="s">
-        <v>334</v>
+      <c r="H175" s="26" t="s">
+        <v>336</v>
       </c>
       <c r="I175" s="6"/>
       <c r="J175" s="1"/>
@@ -8635,23 +8650,23 @@
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="17.25">
       <c r="A176" s="5"/>
       <c r="B176" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C176" s="2">
         <v>17</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E176" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="F176" s="17" t="s">
-        <v>27</v>
+        <v>337</v>
+      </c>
+      <c r="E176" s="29" t="s">
+        <v>338</v>
+      </c>
+      <c r="F176" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G176" s="6"/>
-      <c r="H176" s="25" t="s">
-        <v>337</v>
+      <c r="H176" s="26" t="s">
+        <v>339</v>
       </c>
       <c r="I176" s="6"/>
       <c r="J176" s="1"/>
@@ -8674,23 +8689,23 @@
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="17.25">
       <c r="A177" s="5"/>
       <c r="B177" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C177" s="2">
         <v>18</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E177" s="28" t="s">
-        <v>339</v>
-      </c>
-      <c r="F177" s="19" t="s">
-        <v>63</v>
+        <v>340</v>
+      </c>
+      <c r="E177" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="F177" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G177" s="6"/>
-      <c r="H177" s="26" t="s">
-        <v>340</v>
+      <c r="H177" s="27" t="s">
+        <v>342</v>
       </c>
       <c r="I177" s="6"/>
       <c r="J177" s="1"/>
@@ -8713,23 +8728,23 @@
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="17.25">
       <c r="A178" s="5"/>
       <c r="B178" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C178" s="2">
         <v>19</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E178" s="28" t="s">
-        <v>342</v>
-      </c>
-      <c r="F178" s="17" t="s">
-        <v>27</v>
+        <v>343</v>
+      </c>
+      <c r="E178" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="F178" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G178" s="6"/>
-      <c r="H178" s="25" t="s">
-        <v>343</v>
+      <c r="H178" s="26" t="s">
+        <v>345</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="1"/>
@@ -8752,23 +8767,23 @@
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="17.25">
       <c r="A179" s="5"/>
       <c r="B179" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C179" s="2">
         <v>20</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E179" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="F179" s="17" t="s">
-        <v>27</v>
+        <v>346</v>
+      </c>
+      <c r="E179" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="F179" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G179" s="6"/>
-      <c r="H179" s="25" t="s">
-        <v>345</v>
+      <c r="H179" s="26" t="s">
+        <v>347</v>
       </c>
       <c r="I179" s="6"/>
       <c r="J179" s="1"/>
@@ -8791,23 +8806,23 @@
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="17.25">
       <c r="A180" s="5"/>
       <c r="B180" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C180" s="2">
         <v>21</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E180" s="28" t="s">
-        <v>347</v>
-      </c>
-      <c r="F180" s="17" t="s">
-        <v>27</v>
+        <v>348</v>
+      </c>
+      <c r="E180" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="F180" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G180" s="6"/>
-      <c r="H180" s="25" t="s">
-        <v>348</v>
+      <c r="H180" s="26" t="s">
+        <v>350</v>
       </c>
       <c r="I180" s="6"/>
       <c r="J180" s="1"/>
@@ -8830,23 +8845,23 @@
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="17.25">
       <c r="A181" s="5"/>
       <c r="B181" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C181" s="2">
         <v>22</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E181" s="28" t="s">
-        <v>350</v>
-      </c>
-      <c r="F181" s="17" t="s">
-        <v>27</v>
+        <v>351</v>
+      </c>
+      <c r="E181" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="F181" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G181" s="6"/>
-      <c r="H181" s="25" t="s">
-        <v>351</v>
+      <c r="H181" s="26" t="s">
+        <v>353</v>
       </c>
       <c r="I181" s="6"/>
       <c r="J181" s="1"/>
@@ -8869,23 +8884,23 @@
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="17.25">
       <c r="A182" s="5"/>
       <c r="B182" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C182" s="2">
         <v>23</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E182" s="28" t="s">
-        <v>353</v>
-      </c>
-      <c r="F182" s="17" t="s">
-        <v>27</v>
+        <v>354</v>
+      </c>
+      <c r="E182" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="F182" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G182" s="6"/>
-      <c r="H182" s="26" t="s">
-        <v>354</v>
+      <c r="H182" s="27" t="s">
+        <v>356</v>
       </c>
       <c r="I182" s="6"/>
       <c r="J182" s="1"/>
@@ -8908,23 +8923,23 @@
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="17.25">
       <c r="A183" s="5"/>
       <c r="B183" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C183" s="2">
         <v>24</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="E183" s="28" t="s">
-        <v>356</v>
-      </c>
-      <c r="F183" s="19" t="s">
-        <v>63</v>
+        <v>357</v>
+      </c>
+      <c r="E183" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="F183" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G183" s="6"/>
-      <c r="H183" s="26" t="s">
-        <v>357</v>
+      <c r="H183" s="27" t="s">
+        <v>359</v>
       </c>
       <c r="I183" s="6"/>
       <c r="J183" s="1"/>
@@ -8947,23 +8962,23 @@
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="17.25">
       <c r="A184" s="5"/>
       <c r="B184" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C184" s="2">
         <v>25</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="E184" s="28" t="s">
-        <v>359</v>
-      </c>
-      <c r="F184" s="19" t="s">
-        <v>63</v>
+        <v>360</v>
+      </c>
+      <c r="E184" s="29" t="s">
+        <v>361</v>
+      </c>
+      <c r="F184" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G184" s="6"/>
-      <c r="H184" s="26" t="s">
-        <v>360</v>
+      <c r="H184" s="27" t="s">
+        <v>362</v>
       </c>
       <c r="I184" s="6"/>
       <c r="J184" s="1"/>
@@ -8986,23 +9001,23 @@
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="17.25">
       <c r="A185" s="5"/>
       <c r="B185" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C185" s="2">
         <v>26</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="E185" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="F185" s="19" t="s">
-        <v>63</v>
+        <v>363</v>
+      </c>
+      <c r="E185" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="F185" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G185" s="6"/>
-      <c r="H185" s="25" t="s">
-        <v>362</v>
+      <c r="H185" s="26" t="s">
+        <v>364</v>
       </c>
       <c r="I185" s="6"/>
       <c r="J185" s="1"/>
@@ -9077,27 +9092,27 @@
       <c r="Y187" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="17.25">
-      <c r="A188" s="27" t="s">
-        <v>363</v>
+      <c r="A188" s="28" t="s">
+        <v>365</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C188" s="2">
         <v>1</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="E188" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="E188" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F188" s="15" t="s">
+      <c r="F188" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G188" s="6"/>
-      <c r="H188" s="25" t="s">
-        <v>365</v>
+      <c r="H188" s="26" t="s">
+        <v>367</v>
       </c>
       <c r="I188" s="6"/>
       <c r="J188" s="1"/>
@@ -9120,23 +9135,23 @@
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="17.25">
       <c r="A189" s="5"/>
       <c r="B189" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C189" s="2">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="E189" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="E189" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F189" s="17" t="s">
-        <v>27</v>
+      <c r="F189" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G189" s="6"/>
-      <c r="H189" s="25" t="s">
-        <v>367</v>
+      <c r="H189" s="26" t="s">
+        <v>369</v>
       </c>
       <c r="I189" s="6"/>
       <c r="J189" s="1"/>
@@ -9159,23 +9174,23 @@
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="17.25">
       <c r="A190" s="5"/>
       <c r="B190" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C190" s="2">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="E190" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="E190" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F190" s="17" t="s">
-        <v>27</v>
+      <c r="F190" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G190" s="6"/>
-      <c r="H190" s="26" t="s">
-        <v>369</v>
+      <c r="H190" s="27" t="s">
+        <v>371</v>
       </c>
       <c r="I190" s="6"/>
       <c r="J190" s="1"/>
@@ -9198,23 +9213,23 @@
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="17.25">
       <c r="A191" s="5"/>
       <c r="B191" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C191" s="2">
         <v>4</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="E191" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="E191" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F191" s="17" t="s">
-        <v>27</v>
+      <c r="F191" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G191" s="6"/>
-      <c r="H191" s="26" t="s">
-        <v>371</v>
+      <c r="H191" s="27" t="s">
+        <v>373</v>
       </c>
       <c r="I191" s="6"/>
       <c r="J191" s="1"/>
@@ -9237,23 +9252,23 @@
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="17.25">
       <c r="A192" s="5"/>
       <c r="B192" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C192" s="2">
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="E192" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="E192" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F192" s="17" t="s">
-        <v>27</v>
+      <c r="F192" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G192" s="6"/>
-      <c r="H192" s="25" t="s">
-        <v>373</v>
+      <c r="H192" s="26" t="s">
+        <v>375</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="1"/>
@@ -9276,23 +9291,23 @@
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="17.25">
       <c r="A193" s="5"/>
       <c r="B193" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C193" s="2">
         <v>6</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E193" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="E193" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F193" s="17" t="s">
-        <v>27</v>
+      <c r="F193" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G193" s="6"/>
-      <c r="H193" s="25" t="s">
-        <v>375</v>
+      <c r="H193" s="26" t="s">
+        <v>377</v>
       </c>
       <c r="I193" s="6"/>
       <c r="J193" s="1"/>
@@ -9315,23 +9330,23 @@
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="17.25">
       <c r="A194" s="5"/>
       <c r="B194" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C194" s="2">
         <v>7</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="E194" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E194" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F194" s="17" t="s">
-        <v>27</v>
+      <c r="F194" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G194" s="6"/>
-      <c r="H194" s="25" t="s">
-        <v>377</v>
+      <c r="H194" s="26" t="s">
+        <v>379</v>
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="1"/>
@@ -9354,23 +9369,23 @@
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="17.25">
       <c r="A195" s="5"/>
       <c r="B195" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C195" s="2">
         <v>8</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E195" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="E195" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F195" s="17" t="s">
-        <v>27</v>
+      <c r="F195" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G195" s="6"/>
-      <c r="H195" s="26" t="s">
-        <v>379</v>
+      <c r="H195" s="27" t="s">
+        <v>381</v>
       </c>
       <c r="I195" s="6"/>
       <c r="J195" s="1"/>
@@ -9393,23 +9408,23 @@
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="17.25">
       <c r="A196" s="5"/>
       <c r="B196" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C196" s="2">
         <v>9</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="E196" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="E196" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F196" s="17" t="s">
-        <v>27</v>
+      <c r="F196" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G196" s="6"/>
-      <c r="H196" s="25" t="s">
-        <v>381</v>
+      <c r="H196" s="26" t="s">
+        <v>383</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="1"/>
@@ -9432,23 +9447,23 @@
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="17.25">
       <c r="A197" s="5"/>
       <c r="B197" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C197" s="2">
         <v>10</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E197" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="E197" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F197" s="17" t="s">
-        <v>27</v>
+      <c r="F197" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G197" s="6"/>
-      <c r="H197" s="25" t="s">
-        <v>383</v>
+      <c r="H197" s="26" t="s">
+        <v>385</v>
       </c>
       <c r="I197" s="6"/>
       <c r="J197" s="1"/>
@@ -9471,23 +9486,23 @@
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="17.25">
       <c r="A198" s="5"/>
       <c r="B198" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C198" s="2">
         <v>11</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E198" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="E198" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F198" s="17" t="s">
-        <v>27</v>
+      <c r="F198" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G198" s="6"/>
-      <c r="H198" s="26" t="s">
-        <v>385</v>
+      <c r="H198" s="27" t="s">
+        <v>387</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="1"/>
@@ -9510,23 +9525,23 @@
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="17.25">
       <c r="A199" s="5"/>
       <c r="B199" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C199" s="2">
         <v>12</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E199" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="E199" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F199" s="17" t="s">
-        <v>27</v>
+      <c r="F199" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G199" s="6"/>
-      <c r="H199" s="25" t="s">
-        <v>387</v>
+      <c r="H199" s="26" t="s">
+        <v>389</v>
       </c>
       <c r="I199" s="6"/>
       <c r="J199" s="1"/>
@@ -9549,23 +9564,23 @@
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="17.25">
       <c r="A200" s="5"/>
       <c r="B200" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C200" s="2">
         <v>13</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E200" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="E200" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F200" s="17" t="s">
-        <v>27</v>
+      <c r="F200" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G200" s="6"/>
-      <c r="H200" s="25" t="s">
-        <v>389</v>
+      <c r="H200" s="26" t="s">
+        <v>391</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="1"/>
@@ -9588,23 +9603,23 @@
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="17.25">
       <c r="A201" s="5"/>
       <c r="B201" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C201" s="2">
         <v>14</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E201" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="E201" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F201" s="17" t="s">
-        <v>27</v>
+      <c r="F201" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G201" s="6"/>
-      <c r="H201" s="25" t="s">
-        <v>391</v>
+      <c r="H201" s="26" t="s">
+        <v>393</v>
       </c>
       <c r="I201" s="6"/>
       <c r="J201" s="1"/>
@@ -9627,23 +9642,23 @@
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="17.25">
       <c r="A202" s="5"/>
       <c r="B202" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C202" s="2">
         <v>15</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="E202" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="E202" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F202" s="17" t="s">
-        <v>27</v>
+      <c r="F202" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G202" s="6"/>
-      <c r="H202" s="26" t="s">
-        <v>393</v>
+      <c r="H202" s="27" t="s">
+        <v>395</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="1"/>
@@ -9666,23 +9681,23 @@
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="17.25">
       <c r="A203" s="5"/>
       <c r="B203" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C203" s="2">
         <v>16</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E203" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="E203" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F203" s="19" t="s">
-        <v>63</v>
+      <c r="F203" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G203" s="6"/>
-      <c r="H203" s="26" t="s">
-        <v>395</v>
+      <c r="H203" s="27" t="s">
+        <v>397</v>
       </c>
       <c r="I203" s="6"/>
       <c r="J203" s="1"/>
@@ -9705,23 +9720,23 @@
     <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="17.25">
       <c r="A204" s="5"/>
       <c r="B204" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C204" s="2">
         <v>17</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E204" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="E204" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F204" s="19" t="s">
-        <v>63</v>
+      <c r="F204" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G204" s="6"/>
-      <c r="H204" s="26" t="s">
-        <v>397</v>
+      <c r="H204" s="27" t="s">
+        <v>399</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="1"/>
@@ -9744,23 +9759,23 @@
     <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="17.25">
       <c r="A205" s="5"/>
       <c r="B205" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C205" s="2">
         <v>18</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="E205" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="E205" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F205" s="19" t="s">
-        <v>63</v>
+      <c r="F205" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G205" s="6"/>
-      <c r="H205" s="26" t="s">
-        <v>399</v>
+      <c r="H205" s="27" t="s">
+        <v>401</v>
       </c>
       <c r="I205" s="6"/>
       <c r="J205" s="1"/>
@@ -9783,23 +9798,23 @@
     <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25">
       <c r="A206" s="5"/>
       <c r="B206" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C206" s="2">
         <v>19</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="E206" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="E206" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F206" s="19" t="s">
-        <v>63</v>
+      <c r="F206" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G206" s="6"/>
-      <c r="H206" s="25" t="s">
-        <v>401</v>
+      <c r="H206" s="26" t="s">
+        <v>403</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="1"/>
@@ -9822,23 +9837,23 @@
     <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="17.25">
       <c r="A207" s="5"/>
       <c r="B207" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C207" s="2">
         <v>20</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E207" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="E207" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F207" s="19" t="s">
-        <v>63</v>
+      <c r="F207" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G207" s="6"/>
-      <c r="H207" s="25" t="s">
-        <v>403</v>
+      <c r="H207" s="26" t="s">
+        <v>405</v>
       </c>
       <c r="I207" s="6"/>
       <c r="J207" s="1"/>
@@ -9861,23 +9876,23 @@
     <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="17.25">
       <c r="A208" s="5"/>
       <c r="B208" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C208" s="2">
         <v>21</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E208" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="E208" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F208" s="19" t="s">
-        <v>63</v>
+      <c r="F208" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G208" s="6"/>
-      <c r="H208" s="26" t="s">
-        <v>405</v>
+      <c r="H208" s="27" t="s">
+        <v>407</v>
       </c>
       <c r="I208" s="6"/>
       <c r="J208" s="1"/>
@@ -9952,27 +9967,27 @@
       <c r="Y210" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25">
-      <c r="A211" s="27" t="s">
-        <v>406</v>
+      <c r="A211" s="28" t="s">
+        <v>408</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C211" s="2">
         <v>1</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="E211" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="E211" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F211" s="15" t="s">
+      <c r="F211" s="16" t="s">
         <v>14</v>
       </c>
       <c r="G211" s="6"/>
-      <c r="H211" s="26" t="s">
-        <v>408</v>
+      <c r="H211" s="27" t="s">
+        <v>410</v>
       </c>
       <c r="I211" s="6"/>
       <c r="J211" s="1"/>
@@ -9995,23 +10010,23 @@
     <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="17.25">
       <c r="A212" s="5"/>
       <c r="B212" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C212" s="2">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="E212" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="E212" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F212" s="17" t="s">
-        <v>27</v>
+      <c r="F212" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G212" s="6"/>
-      <c r="H212" s="25" t="s">
-        <v>410</v>
+      <c r="H212" s="26" t="s">
+        <v>412</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="1"/>
@@ -10034,23 +10049,23 @@
     <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25">
       <c r="A213" s="5"/>
       <c r="B213" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C213" s="2">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="E213" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="E213" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F213" s="17" t="s">
-        <v>27</v>
+      <c r="F213" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G213" s="6"/>
-      <c r="H213" s="25" t="s">
-        <v>412</v>
+      <c r="H213" s="26" t="s">
+        <v>414</v>
       </c>
       <c r="I213" s="6"/>
       <c r="J213" s="1"/>
@@ -10073,23 +10088,23 @@
     <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="17.25">
       <c r="A214" s="5"/>
       <c r="B214" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C214" s="2">
         <v>4</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E214" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="E214" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F214" s="17" t="s">
-        <v>27</v>
+      <c r="F214" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G214" s="6"/>
-      <c r="H214" s="25" t="s">
-        <v>414</v>
+      <c r="H214" s="26" t="s">
+        <v>416</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="1"/>
@@ -10112,23 +10127,23 @@
     <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25">
       <c r="A215" s="5"/>
       <c r="B215" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C215" s="2">
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="E215" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="E215" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F215" s="17" t="s">
-        <v>27</v>
+      <c r="F215" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="G215" s="6"/>
-      <c r="H215" s="25" t="s">
-        <v>416</v>
+      <c r="H215" s="26" t="s">
+        <v>418</v>
       </c>
       <c r="I215" s="6"/>
       <c r="J215" s="1"/>
@@ -10151,23 +10166,23 @@
     <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="17.25">
       <c r="A216" s="5"/>
       <c r="B216" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C216" s="2">
         <v>6</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E216" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="E216" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F216" s="19" t="s">
-        <v>63</v>
+      <c r="F216" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G216" s="6"/>
-      <c r="H216" s="25" t="s">
-        <v>418</v>
+      <c r="H216" s="26" t="s">
+        <v>420</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="1"/>
